--- a/data/rules/pickLists.xlsx
+++ b/data/rules/pickLists.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cloned repos\python-components\data\rules\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB9072B7-1C55-4F79-9CA0-20D5899934FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCDE7D64-EA37-48E2-AEC0-B55504109B6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2097" uniqueCount="726">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2099" uniqueCount="727">
   <si>
     <t>Path</t>
   </si>
@@ -2198,6 +2198,9 @@
   </si>
   <si>
     <t>Floating Storage Unit</t>
+  </si>
+  <si>
+    <t>XK</t>
   </si>
 </sst>
 </file>
@@ -3626,7 +3629,7 @@
         <v>67</v>
       </c>
       <c r="B67" s="14" t="s">
-        <v>70</v>
+        <v>509</v>
       </c>
       <c r="C67" s="14"/>
       <c r="D67" s="14"/>
@@ -6900,7 +6903,7 @@
         <v>145</v>
       </c>
       <c r="B359" s="14" t="s">
-        <v>391</v>
+        <v>726</v>
       </c>
       <c r="C359" s="14"/>
       <c r="D359" s="14"/>
@@ -6911,7 +6914,7 @@
         <v>145</v>
       </c>
       <c r="B360" s="14" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C360" s="14"/>
       <c r="D360" s="14"/>
@@ -6922,7 +6925,7 @@
         <v>145</v>
       </c>
       <c r="B361" s="14" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C361" s="14"/>
       <c r="D361" s="14"/>
@@ -6933,29 +6936,29 @@
         <v>145</v>
       </c>
       <c r="B362" s="14" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C362" s="14"/>
       <c r="D362" s="14"/>
       <c r="E362" s="14"/>
     </row>
     <row r="363" spans="1:5" ht="15" thickBot="1">
-      <c r="A363" s="21" t="s">
-        <v>395</v>
+      <c r="A363" s="14" t="s">
+        <v>145</v>
       </c>
       <c r="B363" s="14" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C363" s="14"/>
       <c r="D363" s="14"/>
       <c r="E363" s="14"/>
     </row>
     <row r="364" spans="1:5" ht="15" thickBot="1">
-      <c r="A364" s="14" t="s">
+      <c r="A364" s="21" t="s">
         <v>395</v>
       </c>
       <c r="B364" s="14" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C364" s="14"/>
       <c r="D364" s="14"/>
@@ -6966,7 +6969,7 @@
         <v>395</v>
       </c>
       <c r="B365" s="14" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C365" s="14"/>
       <c r="D365" s="14"/>
@@ -6977,7 +6980,7 @@
         <v>395</v>
       </c>
       <c r="B366" s="14" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C366" s="14"/>
       <c r="D366" s="14"/>
@@ -6988,7 +6991,7 @@
         <v>395</v>
       </c>
       <c r="B367" s="14" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C367" s="14"/>
       <c r="D367" s="14"/>
@@ -6999,7 +7002,7 @@
         <v>395</v>
       </c>
       <c r="B368" s="14" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C368" s="14"/>
       <c r="D368" s="14"/>
@@ -7010,7 +7013,7 @@
         <v>395</v>
       </c>
       <c r="B369" s="14" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C369" s="14"/>
       <c r="D369" s="14"/>
@@ -7021,36 +7024,34 @@
         <v>395</v>
       </c>
       <c r="B370" s="14" t="s">
-        <v>680</v>
+        <v>402</v>
       </c>
       <c r="C370" s="14"/>
       <c r="D370" s="14"/>
       <c r="E370" s="14"/>
     </row>
-    <row r="371" spans="1:5" ht="29.5" thickBot="1">
-      <c r="A371" s="21" t="s">
-        <v>403</v>
+    <row r="371" spans="1:5" ht="15" thickBot="1">
+      <c r="A371" s="14" t="s">
+        <v>395</v>
       </c>
       <c r="B371" s="14" t="s">
-        <v>404</v>
+        <v>680</v>
       </c>
       <c r="C371" s="14"/>
       <c r="D371" s="14"/>
-      <c r="E371" s="14" t="s">
-        <v>405</v>
-      </c>
+      <c r="E371" s="14"/>
     </row>
     <row r="372" spans="1:5" ht="29.5" thickBot="1">
       <c r="A372" s="21" t="s">
         <v>403</v>
       </c>
       <c r="B372" s="14" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C372" s="14"/>
       <c r="D372" s="14"/>
       <c r="E372" s="14" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="373" spans="1:5" ht="29.5" thickBot="1">
@@ -7058,12 +7059,12 @@
         <v>403</v>
       </c>
       <c r="B373" s="14" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C373" s="14"/>
       <c r="D373" s="14"/>
       <c r="E373" s="14" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="374" spans="1:5" ht="29.5" thickBot="1">
@@ -7071,12 +7072,12 @@
         <v>403</v>
       </c>
       <c r="B374" s="14" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C374" s="14"/>
       <c r="D374" s="14"/>
       <c r="E374" s="14" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="375" spans="1:5" ht="29.5" thickBot="1">
@@ -7084,112 +7085,112 @@
         <v>403</v>
       </c>
       <c r="B375" s="14" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C375" s="14"/>
       <c r="D375" s="14"/>
       <c r="E375" s="14" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="376" spans="1:5" ht="44" thickBot="1">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="376" spans="1:5" ht="29.5" thickBot="1">
       <c r="A376" s="21" t="s">
         <v>403</v>
       </c>
       <c r="B376" s="14" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C376" s="14"/>
       <c r="D376" s="14"/>
       <c r="E376" s="14" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="377" spans="1:5" ht="29.5" thickBot="1">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="377" spans="1:5" ht="44" thickBot="1">
       <c r="A377" s="21" t="s">
         <v>403</v>
       </c>
       <c r="B377" s="14" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C377" s="14"/>
       <c r="D377" s="14"/>
       <c r="E377" s="14" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="378" spans="1:5" ht="15" thickBot="1">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="378" spans="1:5" ht="29.5" thickBot="1">
       <c r="A378" s="21" t="s">
         <v>403</v>
       </c>
       <c r="B378" s="14" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C378" s="14"/>
       <c r="D378" s="14"/>
-      <c r="E378" s="14"/>
-    </row>
-    <row r="379" spans="1:5" ht="29.5" thickBot="1">
+      <c r="E378" s="14" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="379" spans="1:5" ht="15" thickBot="1">
       <c r="A379" s="21" t="s">
         <v>403</v>
       </c>
       <c r="B379" s="14" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C379" s="14"/>
       <c r="D379" s="14"/>
-      <c r="E379" s="14" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="380" spans="1:5" ht="15" thickBot="1">
+      <c r="E379" s="14"/>
+    </row>
+    <row r="380" spans="1:5" ht="29.5" thickBot="1">
       <c r="A380" s="21" t="s">
         <v>403</v>
       </c>
       <c r="B380" s="14" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C380" s="14"/>
       <c r="D380" s="14"/>
-      <c r="E380" s="14"/>
-    </row>
-    <row r="381" spans="1:5" ht="29.5" thickBot="1">
+      <c r="E380" s="14" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="381" spans="1:5" ht="15" thickBot="1">
       <c r="A381" s="21" t="s">
-        <v>422</v>
+        <v>403</v>
       </c>
       <c r="B381" s="14" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C381" s="14"/>
       <c r="D381" s="14"/>
-      <c r="E381" s="14" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="382" spans="1:5" ht="15" thickBot="1">
-      <c r="A382" s="14" t="s">
+      <c r="E381" s="14"/>
+    </row>
+    <row r="382" spans="1:5" ht="29.5" thickBot="1">
+      <c r="A382" s="21" t="s">
         <v>422</v>
       </c>
       <c r="B382" s="14" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C382" s="14"/>
       <c r="D382" s="14"/>
       <c r="E382" s="14" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="383" spans="1:5" ht="29.5" thickBot="1">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="383" spans="1:5" ht="15" thickBot="1">
       <c r="A383" s="14" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="B383" s="14" t="s">
-        <v>68</v>
+        <v>425</v>
       </c>
       <c r="C383" s="14"/>
       <c r="D383" s="14"/>
       <c r="E383" s="14" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="384" spans="1:5" ht="29.5" thickBot="1">
@@ -7197,12 +7198,12 @@
         <v>427</v>
       </c>
       <c r="B384" s="14" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="C384" s="14"/>
       <c r="D384" s="14"/>
       <c r="E384" s="14" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="385" spans="1:5" ht="29.5" thickBot="1">
@@ -7210,12 +7211,12 @@
         <v>427</v>
       </c>
       <c r="B385" s="14" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C385" s="14"/>
       <c r="D385" s="14"/>
       <c r="E385" s="14" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="386" spans="1:5" ht="29.5" thickBot="1">
@@ -7223,12 +7224,12 @@
         <v>427</v>
       </c>
       <c r="B386" s="14" t="s">
-        <v>431</v>
+        <v>76</v>
       </c>
       <c r="C386" s="14"/>
       <c r="D386" s="14"/>
       <c r="E386" s="14" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="387" spans="1:5" ht="29.5" thickBot="1">
@@ -7236,44 +7237,46 @@
         <v>427</v>
       </c>
       <c r="B387" s="14" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C387" s="14"/>
       <c r="D387" s="14"/>
       <c r="E387" s="14" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="388" spans="1:5" ht="15" thickBot="1">
-      <c r="A388" s="21" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="388" spans="1:5" ht="29.5" thickBot="1">
+      <c r="A388" s="14" t="s">
         <v>427</v>
       </c>
       <c r="B388" s="14" t="s">
-        <v>30</v>
+        <v>433</v>
       </c>
       <c r="C388" s="14"/>
       <c r="D388" s="14"/>
       <c r="E388" s="14" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="389" spans="1:5" ht="29.5" thickBot="1">
-      <c r="A389" s="14" t="s">
-        <v>436</v>
+        <v>434</v>
+      </c>
+    </row>
+    <row r="389" spans="1:5" ht="15" thickBot="1">
+      <c r="A389" s="21" t="s">
+        <v>427</v>
       </c>
       <c r="B389" s="14" t="s">
-        <v>681</v>
+        <v>30</v>
       </c>
       <c r="C389" s="14"/>
       <c r="D389" s="14"/>
-      <c r="E389" s="14"/>
+      <c r="E389" s="14" t="s">
+        <v>435</v>
+      </c>
     </row>
     <row r="390" spans="1:5" ht="29.5" thickBot="1">
       <c r="A390" s="14" t="s">
         <v>436</v>
       </c>
       <c r="B390" s="14" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="C390" s="14"/>
       <c r="D390" s="14"/>
@@ -7284,7 +7287,7 @@
         <v>436</v>
       </c>
       <c r="B391" s="14" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="C391" s="14"/>
       <c r="D391" s="14"/>
@@ -7295,18 +7298,18 @@
         <v>436</v>
       </c>
       <c r="B392" s="14" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="C392" s="14"/>
       <c r="D392" s="14"/>
       <c r="E392" s="14"/>
     </row>
-    <row r="393" spans="1:5" ht="15" thickBot="1">
+    <row r="393" spans="1:5" ht="29.5" thickBot="1">
       <c r="A393" s="14" t="s">
         <v>436</v>
       </c>
       <c r="B393" s="14" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="C393" s="14"/>
       <c r="D393" s="14"/>
@@ -7317,40 +7320,40 @@
         <v>436</v>
       </c>
       <c r="B394" s="14" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="C394" s="14"/>
       <c r="D394" s="14"/>
       <c r="E394" s="14"/>
     </row>
-    <row r="395" spans="1:5" ht="29.5" thickBot="1">
+    <row r="395" spans="1:5" ht="15" thickBot="1">
       <c r="A395" s="14" t="s">
         <v>436</v>
       </c>
       <c r="B395" s="14" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C395" s="14"/>
       <c r="D395" s="14"/>
       <c r="E395" s="14"/>
     </row>
-    <row r="396" spans="1:5" ht="15" thickBot="1">
+    <row r="396" spans="1:5" ht="29.5" thickBot="1">
       <c r="A396" s="14" t="s">
         <v>436</v>
       </c>
       <c r="B396" s="14" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="C396" s="14"/>
       <c r="D396" s="14"/>
       <c r="E396" s="14"/>
     </row>
-    <row r="397" spans="1:5" ht="29.5" thickBot="1">
+    <row r="397" spans="1:5" ht="15" thickBot="1">
       <c r="A397" s="14" t="s">
         <v>436</v>
       </c>
       <c r="B397" s="14" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="C397" s="14"/>
       <c r="D397" s="14"/>
@@ -7361,18 +7364,18 @@
         <v>436</v>
       </c>
       <c r="B398" s="14" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="C398" s="14"/>
       <c r="D398" s="14"/>
       <c r="E398" s="14"/>
     </row>
-    <row r="399" spans="1:5" ht="15" thickBot="1">
+    <row r="399" spans="1:5" ht="29.5" thickBot="1">
       <c r="A399" s="14" t="s">
         <v>436</v>
       </c>
       <c r="B399" s="14" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="C399" s="14"/>
       <c r="D399" s="14"/>
@@ -7383,7 +7386,7 @@
         <v>436</v>
       </c>
       <c r="B400" s="14" t="s">
-        <v>720</v>
+        <v>691</v>
       </c>
       <c r="C400" s="14"/>
       <c r="D400" s="14"/>
@@ -7394,7 +7397,7 @@
         <v>436</v>
       </c>
       <c r="B401" s="14" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="C401" s="14"/>
       <c r="D401" s="14"/>
@@ -7405,36 +7408,34 @@
         <v>436</v>
       </c>
       <c r="B402" s="14" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="C402" s="14"/>
       <c r="D402" s="14"/>
       <c r="E402" s="14"/>
     </row>
-    <row r="403" spans="1:5" ht="29.5" thickBot="1">
-      <c r="A403" s="21" t="s">
-        <v>437</v>
+    <row r="403" spans="1:5" ht="15" thickBot="1">
+      <c r="A403" s="14" t="s">
+        <v>436</v>
       </c>
       <c r="B403" s="14" t="s">
-        <v>438</v>
+        <v>722</v>
       </c>
       <c r="C403" s="14"/>
       <c r="D403" s="14"/>
-      <c r="E403" s="14" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="404" spans="1:5" ht="15" thickBot="1">
+      <c r="E403" s="14"/>
+    </row>
+    <row r="404" spans="1:5" ht="29.5" thickBot="1">
       <c r="A404" s="21" t="s">
         <v>437</v>
       </c>
       <c r="B404" s="14" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C404" s="14"/>
       <c r="D404" s="14"/>
       <c r="E404" s="14" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="405" spans="1:5" ht="15" thickBot="1">
@@ -7442,12 +7443,12 @@
         <v>437</v>
       </c>
       <c r="B405" s="14" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C405" s="14"/>
       <c r="D405" s="14"/>
       <c r="E405" s="14" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="406" spans="1:5" ht="15" thickBot="1">
@@ -7455,12 +7456,12 @@
         <v>437</v>
       </c>
       <c r="B406" s="14" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C406" s="14"/>
       <c r="D406" s="14"/>
       <c r="E406" s="14" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="407" spans="1:5" ht="15" thickBot="1">
@@ -7468,25 +7469,25 @@
         <v>437</v>
       </c>
       <c r="B407" s="14" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C407" s="14"/>
       <c r="D407" s="14"/>
       <c r="E407" s="14" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="408" spans="1:5" ht="29.5" thickBot="1">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="408" spans="1:5" ht="15" thickBot="1">
       <c r="A408" s="21" t="s">
         <v>437</v>
       </c>
       <c r="B408" s="14" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C408" s="14"/>
       <c r="D408" s="14"/>
       <c r="E408" s="14" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="409" spans="1:5" ht="29.5" thickBot="1">
@@ -7494,25 +7495,25 @@
         <v>437</v>
       </c>
       <c r="B409" s="14" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C409" s="14"/>
       <c r="D409" s="14"/>
       <c r="E409" s="14" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="410" spans="1:5" ht="15" thickBot="1">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="410" spans="1:5" ht="29.5" thickBot="1">
       <c r="A410" s="21" t="s">
         <v>437</v>
       </c>
       <c r="B410" s="14" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C410" s="14"/>
       <c r="D410" s="14"/>
       <c r="E410" s="14" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="411" spans="1:5" ht="15" thickBot="1">
@@ -7520,25 +7521,25 @@
         <v>437</v>
       </c>
       <c r="B411" s="14" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C411" s="14"/>
       <c r="D411" s="14"/>
       <c r="E411" s="14" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="412" spans="1:5" ht="29.5" thickBot="1">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="412" spans="1:5" ht="15" thickBot="1">
       <c r="A412" s="21" t="s">
         <v>437</v>
       </c>
       <c r="B412" s="14" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C412" s="14"/>
       <c r="D412" s="14"/>
       <c r="E412" s="14" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="413" spans="1:5" ht="29.5" thickBot="1">
@@ -7546,12 +7547,12 @@
         <v>437</v>
       </c>
       <c r="B413" s="14" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C413" s="14"/>
       <c r="D413" s="14"/>
       <c r="E413" s="14" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="414" spans="1:5" ht="29.5" thickBot="1">
@@ -7559,73 +7560,73 @@
         <v>437</v>
       </c>
       <c r="B414" s="14" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C414" s="14"/>
       <c r="D414" s="14"/>
       <c r="E414" s="14" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="415" spans="1:5" ht="15" thickBot="1">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="415" spans="1:5" ht="29.5" thickBot="1">
       <c r="A415" s="21" t="s">
         <v>437</v>
       </c>
       <c r="B415" s="14" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C415" s="14"/>
       <c r="D415" s="14"/>
-      <c r="E415" s="14"/>
-    </row>
-    <row r="416" spans="1:5" ht="29.5" thickBot="1">
+      <c r="E415" s="14" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="416" spans="1:5" ht="15" thickBot="1">
       <c r="A416" s="21" t="s">
         <v>437</v>
       </c>
       <c r="B416" s="14" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C416" s="14"/>
       <c r="D416" s="14"/>
-      <c r="E416" s="14" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="417" spans="1:5" ht="15" thickBot="1">
+      <c r="E416" s="14"/>
+    </row>
+    <row r="417" spans="1:5" ht="29.5" thickBot="1">
       <c r="A417" s="21" t="s">
         <v>437</v>
       </c>
       <c r="B417" s="14" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C417" s="14"/>
       <c r="D417" s="14"/>
-      <c r="E417" s="14"/>
-    </row>
-    <row r="418" spans="1:5" ht="29.5" thickBot="1">
+      <c r="E417" s="14" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="418" spans="1:5" ht="15" thickBot="1">
       <c r="A418" s="21" t="s">
         <v>437</v>
       </c>
       <c r="B418" s="14" t="s">
-        <v>30</v>
+        <v>465</v>
       </c>
       <c r="C418" s="14"/>
       <c r="D418" s="14"/>
-      <c r="E418" s="14" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="419" spans="1:5" ht="15" thickBot="1">
-      <c r="A419" s="14" t="s">
-        <v>467</v>
+      <c r="E418" s="14"/>
+    </row>
+    <row r="419" spans="1:5" ht="29.5" thickBot="1">
+      <c r="A419" s="21" t="s">
+        <v>437</v>
       </c>
       <c r="B419" s="14" t="s">
-        <v>468</v>
+        <v>30</v>
       </c>
       <c r="C419" s="14"/>
       <c r="D419" s="14"/>
       <c r="E419" s="14" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
     </row>
     <row r="420" spans="1:5" ht="15" thickBot="1">
@@ -7633,18 +7634,20 @@
         <v>467</v>
       </c>
       <c r="B420" s="14" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C420" s="14"/>
       <c r="D420" s="14"/>
-      <c r="E420" s="14"/>
+      <c r="E420" s="14" t="s">
+        <v>469</v>
+      </c>
     </row>
     <row r="421" spans="1:5" ht="15" thickBot="1">
       <c r="A421" s="14" t="s">
         <v>467</v>
       </c>
       <c r="B421" s="14" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C421" s="14"/>
       <c r="D421" s="14"/>
@@ -7655,7 +7658,7 @@
         <v>467</v>
       </c>
       <c r="B422" s="14" t="s">
-        <v>692</v>
+        <v>471</v>
       </c>
       <c r="C422" s="14"/>
       <c r="D422" s="14"/>
@@ -7663,39 +7666,37 @@
     </row>
     <row r="423" spans="1:5" ht="15" thickBot="1">
       <c r="A423" s="14" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="B423" s="14" t="s">
-        <v>473</v>
+        <v>692</v>
       </c>
       <c r="C423" s="14"/>
       <c r="D423" s="14"/>
       <c r="E423" s="14"/>
     </row>
-    <row r="424" spans="1:5" ht="29.5" thickBot="1">
+    <row r="424" spans="1:5" ht="15" thickBot="1">
       <c r="A424" s="14" t="s">
         <v>472</v>
       </c>
       <c r="B424" s="14" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C424" s="14"/>
       <c r="D424" s="14"/>
-      <c r="E424" s="14" t="s">
-        <v>475</v>
-      </c>
+      <c r="E424" s="14"/>
     </row>
     <row r="425" spans="1:5" ht="29.5" thickBot="1">
       <c r="A425" s="14" t="s">
         <v>472</v>
       </c>
       <c r="B425" s="14" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C425" s="14"/>
       <c r="D425" s="14"/>
       <c r="E425" s="14" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="426" spans="1:5" ht="29.5" thickBot="1">
@@ -7703,12 +7704,12 @@
         <v>472</v>
       </c>
       <c r="B426" s="14" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C426" s="14"/>
       <c r="D426" s="14"/>
       <c r="E426" s="14" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="427" spans="1:5" ht="29.5" thickBot="1">
@@ -7716,12 +7717,12 @@
         <v>472</v>
       </c>
       <c r="B427" s="14" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C427" s="14"/>
       <c r="D427" s="14"/>
       <c r="E427" s="14" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="428" spans="1:5" ht="29.5" thickBot="1">
@@ -7729,12 +7730,12 @@
         <v>472</v>
       </c>
       <c r="B428" s="14" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C428" s="14"/>
       <c r="D428" s="14"/>
       <c r="E428" s="14" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="429" spans="1:5" ht="29.5" thickBot="1">
@@ -7742,49 +7743,49 @@
         <v>472</v>
       </c>
       <c r="B429" s="14" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C429" s="14"/>
       <c r="D429" s="14"/>
       <c r="E429" s="14" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="430" spans="1:5" ht="15" thickBot="1">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="430" spans="1:5" ht="29.5" thickBot="1">
       <c r="A430" s="14" t="s">
         <v>472</v>
       </c>
       <c r="B430" s="14" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C430" s="14"/>
       <c r="D430" s="14"/>
-      <c r="E430" s="14"/>
-    </row>
-    <row r="431" spans="1:5" ht="29.5" thickBot="1">
+      <c r="E430" s="14" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="431" spans="1:5" ht="15" thickBot="1">
       <c r="A431" s="14" t="s">
         <v>472</v>
       </c>
       <c r="B431" s="14" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C431" s="14"/>
       <c r="D431" s="14"/>
-      <c r="E431" s="14" t="s">
-        <v>488</v>
-      </c>
+      <c r="E431" s="14"/>
     </row>
     <row r="432" spans="1:5" ht="29.5" thickBot="1">
       <c r="A432" s="14" t="s">
         <v>472</v>
       </c>
       <c r="B432" s="14" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C432" s="14"/>
       <c r="D432" s="14"/>
       <c r="E432" s="14" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="433" spans="1:5" ht="29.5" thickBot="1">
@@ -7792,31 +7793,33 @@
         <v>472</v>
       </c>
       <c r="B433" s="14" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C433" s="14"/>
       <c r="D433" s="14"/>
       <c r="E433" s="14" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="434" spans="1:5" ht="15" thickBot="1">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="434" spans="1:5" ht="29.5" thickBot="1">
       <c r="A434" s="14" t="s">
         <v>472</v>
       </c>
       <c r="B434" s="14" t="s">
-        <v>693</v>
+        <v>491</v>
       </c>
       <c r="C434" s="14"/>
       <c r="D434" s="14"/>
-      <c r="E434" s="14"/>
+      <c r="E434" s="14" t="s">
+        <v>492</v>
+      </c>
     </row>
     <row r="435" spans="1:5" ht="15" thickBot="1">
       <c r="A435" s="14" t="s">
         <v>472</v>
       </c>
       <c r="B435" s="14" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="C435" s="14"/>
       <c r="D435" s="14"/>
@@ -7827,36 +7830,34 @@
         <v>472</v>
       </c>
       <c r="B436" s="14" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="C436" s="14"/>
       <c r="D436" s="14"/>
       <c r="E436" s="14"/>
     </row>
-    <row r="437" spans="1:5" ht="29.5" thickBot="1">
+    <row r="437" spans="1:5" ht="15" thickBot="1">
       <c r="A437" s="14" t="s">
         <v>472</v>
       </c>
       <c r="B437" s="14" t="s">
-        <v>30</v>
+        <v>695</v>
       </c>
       <c r="C437" s="14"/>
       <c r="D437" s="14"/>
-      <c r="E437" s="14" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="438" spans="1:5" ht="15" thickBot="1">
+      <c r="E437" s="14"/>
+    </row>
+    <row r="438" spans="1:5" ht="29.5" thickBot="1">
       <c r="A438" s="14" t="s">
-        <v>494</v>
+        <v>472</v>
       </c>
       <c r="B438" s="14" t="s">
-        <v>495</v>
+        <v>30</v>
       </c>
       <c r="C438" s="14"/>
       <c r="D438" s="14"/>
       <c r="E438" s="14" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
     </row>
     <row r="439" spans="1:5" ht="15" thickBot="1">
@@ -7864,12 +7865,12 @@
         <v>494</v>
       </c>
       <c r="B439" s="14" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C439" s="14"/>
       <c r="D439" s="14"/>
       <c r="E439" s="14" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="440" spans="1:5" ht="15" thickBot="1">
@@ -7877,25 +7878,25 @@
         <v>494</v>
       </c>
       <c r="B440" s="14" t="s">
-        <v>15</v>
+        <v>497</v>
       </c>
       <c r="C440" s="14"/>
       <c r="D440" s="14"/>
       <c r="E440" s="14" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="441" spans="1:5" ht="15" thickBot="1">
       <c r="A441" s="14" t="s">
-        <v>696</v>
+        <v>494</v>
       </c>
       <c r="B441" s="14" t="s">
-        <v>697</v>
+        <v>15</v>
       </c>
       <c r="C441" s="14"/>
       <c r="D441" s="14"/>
       <c r="E441" s="14" t="s">
-        <v>698</v>
+        <v>499</v>
       </c>
     </row>
     <row r="442" spans="1:5" ht="15" thickBot="1">
@@ -7903,12 +7904,12 @@
         <v>696</v>
       </c>
       <c r="B442" s="14" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="C442" s="14"/>
       <c r="D442" s="14"/>
       <c r="E442" s="14" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
     </row>
     <row r="443" spans="1:5" ht="15" thickBot="1">
@@ -7916,12 +7917,12 @@
         <v>696</v>
       </c>
       <c r="B443" s="14" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="C443" s="14"/>
       <c r="D443" s="14"/>
       <c r="E443" s="14" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
     </row>
     <row r="444" spans="1:5" ht="15" thickBot="1">
@@ -7929,90 +7930,90 @@
         <v>696</v>
       </c>
       <c r="B444" s="14" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="C444" s="14"/>
       <c r="D444" s="14"/>
       <c r="E444" s="14" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="445" spans="1:5" ht="29.5" thickBot="1">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="445" spans="1:5" ht="15" thickBot="1">
       <c r="A445" s="14" t="s">
-        <v>500</v>
+        <v>696</v>
       </c>
       <c r="B445" s="14" t="s">
-        <v>135</v>
+        <v>703</v>
       </c>
       <c r="C445" s="14"/>
       <c r="D445" s="14"/>
       <c r="E445" s="14" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="446" spans="1:5" ht="15" thickBot="1">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="446" spans="1:5" ht="29.5" thickBot="1">
       <c r="A446" s="14" t="s">
         <v>500</v>
       </c>
       <c r="B446" s="14" t="s">
-        <v>404</v>
+        <v>135</v>
       </c>
       <c r="C446" s="14"/>
       <c r="D446" s="14"/>
       <c r="E446" s="14" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="447" spans="1:5" ht="29.5" thickBot="1">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="447" spans="1:5" ht="15" thickBot="1">
       <c r="A447" s="14" t="s">
         <v>500</v>
       </c>
       <c r="B447" s="14" t="s">
-        <v>137</v>
+        <v>404</v>
       </c>
       <c r="C447" s="14"/>
       <c r="D447" s="14"/>
       <c r="E447" s="14" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="448" spans="1:5" ht="15" thickBot="1">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="448" spans="1:5" ht="29.5" thickBot="1">
       <c r="A448" s="14" t="s">
         <v>500</v>
       </c>
       <c r="B448" s="14" t="s">
-        <v>504</v>
+        <v>137</v>
       </c>
       <c r="C448" s="14"/>
       <c r="D448" s="14"/>
       <c r="E448" s="14" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="449" spans="1:5" ht="44" thickBot="1">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="449" spans="1:5" ht="15" thickBot="1">
       <c r="A449" s="14" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="B449" s="14" t="s">
-        <v>68</v>
+        <v>504</v>
       </c>
       <c r="C449" s="14"/>
       <c r="D449" s="14"/>
       <c r="E449" s="14" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="450" spans="1:5" ht="29.5" thickBot="1">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="450" spans="1:5" ht="44" thickBot="1">
       <c r="A450" s="14" t="s">
         <v>506</v>
       </c>
       <c r="B450" s="14" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C450" s="14"/>
       <c r="D450" s="14"/>
       <c r="E450" s="14" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="451" spans="1:5" ht="29.5" thickBot="1">
@@ -8020,12 +8021,12 @@
         <v>506</v>
       </c>
       <c r="B451" s="14" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C451" s="14"/>
       <c r="D451" s="14"/>
       <c r="E451" s="14" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="452" spans="1:5" ht="29.5" thickBot="1">
@@ -8033,25 +8034,25 @@
         <v>506</v>
       </c>
       <c r="B452" s="14" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C452" s="14"/>
       <c r="D452" s="14"/>
       <c r="E452" s="14" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="453" spans="1:5" ht="44" thickBot="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="453" spans="1:5" ht="29.5" thickBot="1">
       <c r="A453" s="14" t="s">
         <v>506</v>
       </c>
       <c r="B453" s="14" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C453" s="14"/>
       <c r="D453" s="14"/>
       <c r="E453" s="14" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="454" spans="1:5" ht="44" thickBot="1">
@@ -8059,12 +8060,12 @@
         <v>506</v>
       </c>
       <c r="B454" s="14" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C454" s="14"/>
       <c r="D454" s="14"/>
       <c r="E454" s="14" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="455" spans="1:5" ht="44" thickBot="1">
@@ -8072,41 +8073,39 @@
         <v>506</v>
       </c>
       <c r="B455" s="14" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C455" s="14"/>
       <c r="D455" s="14"/>
       <c r="E455" s="14" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="456" spans="1:5" ht="44" thickBot="1">
+      <c r="A456" s="14" t="s">
+        <v>506</v>
+      </c>
+      <c r="B456" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="C456" s="14"/>
+      <c r="D456" s="14"/>
+      <c r="E456" s="14" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="456" spans="1:5" ht="15" thickBot="1">
-      <c r="A456" s="14" t="s">
-        <v>507</v>
-      </c>
-      <c r="B456" s="14" t="s">
-        <v>508</v>
-      </c>
-      <c r="C456" s="14" t="s">
-        <v>506</v>
-      </c>
-      <c r="D456" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="E456" s="14"/>
     </row>
     <row r="457" spans="1:5" ht="15" thickBot="1">
       <c r="A457" s="14" t="s">
         <v>507</v>
       </c>
       <c r="B457" s="14" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C457" s="14" t="s">
         <v>506</v>
       </c>
       <c r="D457" s="15" t="s">
-        <v>509</v>
+        <v>68</v>
       </c>
       <c r="E457" s="14"/>
     </row>
@@ -8115,13 +8114,13 @@
         <v>507</v>
       </c>
       <c r="B458" s="14" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C458" s="14" t="s">
         <v>506</v>
       </c>
       <c r="D458" s="15" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="E458" s="14"/>
     </row>
@@ -8130,13 +8129,13 @@
         <v>507</v>
       </c>
       <c r="B459" s="14" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C459" s="14" t="s">
         <v>506</v>
       </c>
       <c r="D459" s="15" t="s">
-        <v>74</v>
+        <v>510</v>
       </c>
       <c r="E459" s="14"/>
     </row>
@@ -8145,7 +8144,7 @@
         <v>507</v>
       </c>
       <c r="B460" s="14" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C460" s="14" t="s">
         <v>506</v>
@@ -8160,7 +8159,7 @@
         <v>507</v>
       </c>
       <c r="B461" s="14" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C461" s="14" t="s">
         <v>506</v>
@@ -8175,7 +8174,7 @@
         <v>507</v>
       </c>
       <c r="B462" s="14" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C462" s="14" t="s">
         <v>506</v>
@@ -8190,7 +8189,7 @@
         <v>507</v>
       </c>
       <c r="B463" s="14" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C463" s="14" t="s">
         <v>506</v>
@@ -8205,13 +8204,13 @@
         <v>507</v>
       </c>
       <c r="B464" s="14" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C464" s="14" t="s">
         <v>506</v>
       </c>
       <c r="D464" s="15" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E464" s="14"/>
     </row>
@@ -8220,43 +8219,43 @@
         <v>507</v>
       </c>
       <c r="B465" s="14" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C465" s="14" t="s">
         <v>506</v>
       </c>
       <c r="D465" s="15" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E465" s="14"/>
     </row>
-    <row r="466" spans="1:5" ht="29.5" thickBot="1">
+    <row r="466" spans="1:5" ht="15" thickBot="1">
       <c r="A466" s="14" t="s">
         <v>507</v>
       </c>
       <c r="B466" s="14" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C466" s="14" t="s">
         <v>506</v>
       </c>
       <c r="D466" s="15" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E466" s="14"/>
     </row>
-    <row r="467" spans="1:5" ht="15" thickBot="1">
+    <row r="467" spans="1:5" ht="29.5" thickBot="1">
       <c r="A467" s="14" t="s">
         <v>507</v>
       </c>
       <c r="B467" s="14" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C467" s="14" t="s">
         <v>506</v>
       </c>
       <c r="D467" s="15" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E467" s="14"/>
     </row>
@@ -8265,7 +8264,7 @@
         <v>507</v>
       </c>
       <c r="B468" s="14" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C468" s="14" t="s">
         <v>506</v>
@@ -8280,7 +8279,7 @@
         <v>507</v>
       </c>
       <c r="B469" s="14" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C469" s="14" t="s">
         <v>506</v>
@@ -8290,43 +8289,45 @@
       </c>
       <c r="E469" s="14"/>
     </row>
-    <row r="470" spans="1:5" ht="29.5" thickBot="1">
+    <row r="470" spans="1:5" ht="15" thickBot="1">
       <c r="A470" s="14" t="s">
-        <v>522</v>
+        <v>507</v>
       </c>
       <c r="B470" s="14" t="s">
-        <v>523</v>
-      </c>
-      <c r="C470" s="14"/>
-      <c r="D470" s="14"/>
-      <c r="E470" s="14" t="s">
-        <v>524</v>
-      </c>
+        <v>521</v>
+      </c>
+      <c r="C470" s="14" t="s">
+        <v>506</v>
+      </c>
+      <c r="D470" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="E470" s="14"/>
     </row>
     <row r="471" spans="1:5" ht="29.5" thickBot="1">
       <c r="A471" s="14" t="s">
         <v>522</v>
       </c>
       <c r="B471" s="14" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="C471" s="14"/>
       <c r="D471" s="14"/>
       <c r="E471" s="14" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="472" spans="1:5" ht="15" thickBot="1">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="472" spans="1:5" ht="29.5" thickBot="1">
       <c r="A472" s="14" t="s">
         <v>522</v>
       </c>
       <c r="B472" s="14" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="C472" s="14"/>
       <c r="D472" s="14"/>
       <c r="E472" s="14" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
     </row>
     <row r="473" spans="1:5" ht="15" thickBot="1">
@@ -8334,12 +8335,12 @@
         <v>522</v>
       </c>
       <c r="B473" s="14" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C473" s="14"/>
       <c r="D473" s="14"/>
       <c r="E473" s="14" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
     </row>
     <row r="474" spans="1:5" ht="15" thickBot="1">
@@ -8347,38 +8348,38 @@
         <v>522</v>
       </c>
       <c r="B474" s="14" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C474" s="14"/>
       <c r="D474" s="14"/>
       <c r="E474" s="14" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="475" spans="1:5" ht="29.5" thickBot="1">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="475" spans="1:5" ht="15" thickBot="1">
       <c r="A475" s="14" t="s">
         <v>522</v>
       </c>
       <c r="B475" s="14" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C475" s="14"/>
       <c r="D475" s="14"/>
       <c r="E475" s="14" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="476" spans="1:5" ht="15" thickBot="1">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="476" spans="1:5" ht="29.5" thickBot="1">
       <c r="A476" s="14" t="s">
         <v>522</v>
       </c>
       <c r="B476" s="14" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C476" s="14"/>
       <c r="D476" s="14"/>
       <c r="E476" s="14" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
     </row>
     <row r="477" spans="1:5" ht="15" thickBot="1">
@@ -8386,12 +8387,12 @@
         <v>522</v>
       </c>
       <c r="B477" s="14" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="C477" s="14"/>
       <c r="D477" s="14"/>
       <c r="E477" s="14" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
     </row>
     <row r="478" spans="1:5" ht="15" thickBot="1">
@@ -8399,51 +8400,51 @@
         <v>522</v>
       </c>
       <c r="B478" s="14" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="C478" s="14"/>
       <c r="D478" s="14"/>
       <c r="E478" s="14" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="479" spans="1:5" ht="29.5" thickBot="1">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="479" spans="1:5" ht="15" thickBot="1">
       <c r="A479" s="14" t="s">
         <v>522</v>
       </c>
       <c r="B479" s="14" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C479" s="14"/>
       <c r="D479" s="14"/>
       <c r="E479" s="14" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="480" spans="1:5" ht="15" thickBot="1">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="480" spans="1:5" ht="29.5" thickBot="1">
       <c r="A480" s="14" t="s">
         <v>522</v>
       </c>
       <c r="B480" s="14" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="C480" s="14"/>
       <c r="D480" s="14"/>
       <c r="E480" s="14" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="481" spans="1:5" ht="29.5" thickBot="1">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="481" spans="1:5" ht="15" thickBot="1">
       <c r="A481" s="14" t="s">
         <v>522</v>
       </c>
       <c r="B481" s="14" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="C481" s="14"/>
       <c r="D481" s="14"/>
       <c r="E481" s="14" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="482" spans="1:5" ht="29.5" thickBot="1">
@@ -8451,12 +8452,12 @@
         <v>522</v>
       </c>
       <c r="B482" s="14" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C482" s="14"/>
       <c r="D482" s="14"/>
       <c r="E482" s="14" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="483" spans="1:5" ht="29.5" thickBot="1">
@@ -8464,12 +8465,12 @@
         <v>522</v>
       </c>
       <c r="B483" s="14" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="C483" s="14"/>
       <c r="D483" s="14"/>
       <c r="E483" s="14" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
     <row r="484" spans="1:5" ht="29.5" thickBot="1">
@@ -8477,25 +8478,25 @@
         <v>522</v>
       </c>
       <c r="B484" s="14" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="C484" s="14"/>
       <c r="D484" s="14"/>
       <c r="E484" s="14" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="485" spans="1:5" ht="15" thickBot="1">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="485" spans="1:5" ht="29.5" thickBot="1">
       <c r="A485" s="14" t="s">
         <v>522</v>
       </c>
       <c r="B485" s="14" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="C485" s="14"/>
       <c r="D485" s="14"/>
       <c r="E485" s="14" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
     </row>
     <row r="486" spans="1:5" ht="15" thickBot="1">
@@ -8503,12 +8504,12 @@
         <v>522</v>
       </c>
       <c r="B486" s="14" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="C486" s="14"/>
       <c r="D486" s="14"/>
       <c r="E486" s="14" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="487" spans="1:5" ht="15" thickBot="1">
@@ -8516,12 +8517,12 @@
         <v>522</v>
       </c>
       <c r="B487" s="14" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="C487" s="14"/>
       <c r="D487" s="14"/>
       <c r="E487" s="14" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
     </row>
     <row r="488" spans="1:5" ht="15" thickBot="1">
@@ -8529,12 +8530,12 @@
         <v>522</v>
       </c>
       <c r="B488" s="14" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="C488" s="14"/>
       <c r="D488" s="14"/>
       <c r="E488" s="14" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
     </row>
     <row r="489" spans="1:5" ht="15" thickBot="1">
@@ -8542,51 +8543,51 @@
         <v>522</v>
       </c>
       <c r="B489" s="14" t="s">
-        <v>30</v>
+        <v>559</v>
       </c>
       <c r="C489" s="14"/>
       <c r="D489" s="14"/>
       <c r="E489" s="14" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="490" spans="1:5" ht="15" thickBot="1">
       <c r="A490" s="14" t="s">
-        <v>562</v>
+        <v>522</v>
       </c>
       <c r="B490" s="14" t="s">
-        <v>563</v>
+        <v>30</v>
       </c>
       <c r="C490" s="14"/>
       <c r="D490" s="14"/>
       <c r="E490" s="14" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="491" spans="1:5" ht="29.5" thickBot="1">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="491" spans="1:5" ht="15" thickBot="1">
       <c r="A491" s="14" t="s">
         <v>562</v>
       </c>
       <c r="B491" s="14" t="s">
-        <v>111</v>
+        <v>563</v>
       </c>
       <c r="C491" s="14"/>
       <c r="D491" s="14"/>
       <c r="E491" s="14" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="492" spans="1:5" ht="15" thickBot="1">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="492" spans="1:5" ht="29.5" thickBot="1">
       <c r="A492" s="14" t="s">
         <v>562</v>
       </c>
       <c r="B492" s="14" t="s">
-        <v>566</v>
+        <v>111</v>
       </c>
       <c r="C492" s="14"/>
       <c r="D492" s="14"/>
       <c r="E492" s="14" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
     </row>
     <row r="493" spans="1:5" ht="15" thickBot="1">
@@ -8594,12 +8595,12 @@
         <v>562</v>
       </c>
       <c r="B493" s="14" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="C493" s="14"/>
       <c r="D493" s="14"/>
       <c r="E493" s="14" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="494" spans="1:5" ht="15" thickBot="1">
@@ -8607,12 +8608,12 @@
         <v>562</v>
       </c>
       <c r="B494" s="14" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="C494" s="14"/>
       <c r="D494" s="14"/>
       <c r="E494" s="14" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
     </row>
     <row r="495" spans="1:5" ht="15" thickBot="1">
@@ -8620,12 +8621,12 @@
         <v>562</v>
       </c>
       <c r="B495" s="14" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="C495" s="14"/>
       <c r="D495" s="14"/>
       <c r="E495" s="14" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
     </row>
     <row r="496" spans="1:5" ht="15" thickBot="1">
@@ -8633,12 +8634,12 @@
         <v>562</v>
       </c>
       <c r="B496" s="14" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="C496" s="14"/>
       <c r="D496" s="14"/>
       <c r="E496" s="14" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="497" spans="1:5" ht="15" thickBot="1">
@@ -8646,12 +8647,12 @@
         <v>562</v>
       </c>
       <c r="B497" s="14" t="s">
-        <v>119</v>
+        <v>574</v>
       </c>
       <c r="C497" s="14"/>
       <c r="D497" s="14"/>
       <c r="E497" s="14" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="498" spans="1:5" ht="15" thickBot="1">
@@ -8659,12 +8660,12 @@
         <v>562</v>
       </c>
       <c r="B498" s="14" t="s">
-        <v>577</v>
+        <v>119</v>
       </c>
       <c r="C498" s="14"/>
       <c r="D498" s="14"/>
       <c r="E498" s="14" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
     </row>
     <row r="499" spans="1:5" ht="15" thickBot="1">
@@ -8672,12 +8673,12 @@
         <v>562</v>
       </c>
       <c r="B499" s="14" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="C499" s="14"/>
       <c r="D499" s="14"/>
       <c r="E499" s="14" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
     </row>
     <row r="500" spans="1:5" ht="15" thickBot="1">
@@ -8685,12 +8686,12 @@
         <v>562</v>
       </c>
       <c r="B500" s="14" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="C500" s="14"/>
       <c r="D500" s="14"/>
       <c r="E500" s="14" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="501" spans="1:5" ht="15" thickBot="1">
@@ -8698,51 +8699,51 @@
         <v>562</v>
       </c>
       <c r="B501" s="14" t="s">
-        <v>115</v>
+        <v>581</v>
       </c>
       <c r="C501" s="14"/>
       <c r="D501" s="14"/>
       <c r="E501" s="14" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="502" spans="1:5" ht="29.5" thickBot="1">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="502" spans="1:5" ht="15" thickBot="1">
       <c r="A502" s="14" t="s">
         <v>562</v>
       </c>
       <c r="B502" s="14" t="s">
-        <v>584</v>
+        <v>115</v>
       </c>
       <c r="C502" s="14"/>
       <c r="D502" s="14"/>
       <c r="E502" s="14" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="503" spans="1:5" ht="15" thickBot="1">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="503" spans="1:5" ht="29.5" thickBot="1">
       <c r="A503" s="14" t="s">
         <v>562</v>
       </c>
       <c r="B503" s="14" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="C503" s="14"/>
       <c r="D503" s="14"/>
       <c r="E503" s="14" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="504" spans="1:5" ht="29.5" thickBot="1">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="504" spans="1:5" ht="15" thickBot="1">
       <c r="A504" s="14" t="s">
         <v>562</v>
       </c>
       <c r="B504" s="14" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="C504" s="14"/>
       <c r="D504" s="14"/>
       <c r="E504" s="14" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
     </row>
     <row r="505" spans="1:5" ht="29.5" thickBot="1">
@@ -8750,12 +8751,12 @@
         <v>562</v>
       </c>
       <c r="B505" s="14" t="s">
-        <v>98</v>
+        <v>588</v>
       </c>
       <c r="C505" s="14"/>
       <c r="D505" s="14"/>
       <c r="E505" s="14" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="506" spans="1:5" ht="29.5" thickBot="1">
@@ -8763,25 +8764,25 @@
         <v>562</v>
       </c>
       <c r="B506" s="14" t="s">
-        <v>30</v>
+        <v>98</v>
       </c>
       <c r="C506" s="14"/>
       <c r="D506" s="14"/>
       <c r="E506" s="14" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="507" spans="1:5" ht="15" thickBot="1">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="507" spans="1:5" ht="29.5" thickBot="1">
       <c r="A507" s="14" t="s">
-        <v>592</v>
+        <v>562</v>
       </c>
       <c r="B507" s="14" t="s">
-        <v>593</v>
+        <v>30</v>
       </c>
       <c r="C507" s="14"/>
       <c r="D507" s="14"/>
       <c r="E507" s="14" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
     </row>
     <row r="508" spans="1:5" ht="15" thickBot="1">
@@ -8789,12 +8790,12 @@
         <v>592</v>
       </c>
       <c r="B508" s="14" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="C508" s="14"/>
       <c r="D508" s="14"/>
       <c r="E508" s="14" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
     </row>
     <row r="509" spans="1:5" ht="15" thickBot="1">
@@ -8802,12 +8803,12 @@
         <v>592</v>
       </c>
       <c r="B509" s="14" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="C509" s="14"/>
       <c r="D509" s="14"/>
       <c r="E509" s="14" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
     </row>
     <row r="510" spans="1:5" ht="15" thickBot="1">
@@ -8815,25 +8816,25 @@
         <v>592</v>
       </c>
       <c r="B510" s="14" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="C510" s="14"/>
       <c r="D510" s="14"/>
       <c r="E510" s="14" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="511" spans="1:5" ht="29.5" thickBot="1">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="511" spans="1:5" ht="15" thickBot="1">
       <c r="A511" s="14" t="s">
-        <v>601</v>
+        <v>592</v>
       </c>
       <c r="B511" s="14" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="C511" s="14"/>
       <c r="D511" s="14"/>
       <c r="E511" s="14" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
     </row>
     <row r="512" spans="1:5" ht="29.5" thickBot="1">
@@ -8841,12 +8842,12 @@
         <v>601</v>
       </c>
       <c r="B512" s="14" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="C512" s="14"/>
       <c r="D512" s="14"/>
       <c r="E512" s="14" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
     </row>
     <row r="513" spans="1:5" ht="29.5" thickBot="1">
@@ -8854,12 +8855,12 @@
         <v>601</v>
       </c>
       <c r="B513" s="14" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="C513" s="14"/>
       <c r="D513" s="14"/>
       <c r="E513" s="14" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
     </row>
     <row r="514" spans="1:5" ht="29.5" thickBot="1">
@@ -8867,25 +8868,25 @@
         <v>601</v>
       </c>
       <c r="B514" s="14" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C514" s="14"/>
       <c r="D514" s="14"/>
       <c r="E514" s="14" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="515" spans="1:5" ht="29.5" thickBot="1">
       <c r="A515" s="14" t="s">
-        <v>610</v>
+        <v>601</v>
       </c>
       <c r="B515" s="14" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="C515" s="14"/>
       <c r="D515" s="14"/>
       <c r="E515" s="14" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="516" spans="1:5" ht="29.5" thickBot="1">
@@ -8893,12 +8894,12 @@
         <v>610</v>
       </c>
       <c r="B516" s="14" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="C516" s="14"/>
       <c r="D516" s="14"/>
       <c r="E516" s="14" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="517" spans="1:5" ht="29.5" thickBot="1">
@@ -8906,31 +8907,33 @@
         <v>610</v>
       </c>
       <c r="B517" s="14" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="C517" s="14"/>
       <c r="D517" s="14"/>
       <c r="E517" s="14" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="518" spans="1:5" ht="15" thickBot="1">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="518" spans="1:5" ht="29.5" thickBot="1">
       <c r="A518" s="14" t="s">
         <v>610</v>
       </c>
       <c r="B518" s="14" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="C518" s="14"/>
       <c r="D518" s="14"/>
-      <c r="E518" s="14"/>
+      <c r="E518" s="14" t="s">
+        <v>616</v>
+      </c>
     </row>
     <row r="519" spans="1:5" ht="15" thickBot="1">
       <c r="A519" s="14" t="s">
         <v>610</v>
       </c>
       <c r="B519" s="14" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C519" s="14"/>
       <c r="D519" s="14"/>
@@ -8941,7 +8944,7 @@
         <v>610</v>
       </c>
       <c r="B520" s="14" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C520" s="14"/>
       <c r="D520" s="14"/>
@@ -8952,7 +8955,7 @@
         <v>610</v>
       </c>
       <c r="B521" s="14" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C521" s="14"/>
       <c r="D521" s="14"/>
@@ -8963,7 +8966,7 @@
         <v>610</v>
       </c>
       <c r="B522" s="14" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C522" s="14"/>
       <c r="D522" s="14"/>
@@ -8974,7 +8977,7 @@
         <v>610</v>
       </c>
       <c r="B523" s="14" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C523" s="14"/>
       <c r="D523" s="14"/>
@@ -8985,7 +8988,7 @@
         <v>610</v>
       </c>
       <c r="B524" s="14" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C524" s="14"/>
       <c r="D524" s="14"/>
@@ -8996,7 +8999,7 @@
         <v>610</v>
       </c>
       <c r="B525" s="14" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C525" s="14"/>
       <c r="D525" s="14"/>
@@ -9007,7 +9010,7 @@
         <v>610</v>
       </c>
       <c r="B526" s="14" t="s">
-        <v>95</v>
+        <v>624</v>
       </c>
       <c r="C526" s="14"/>
       <c r="D526" s="14"/>
@@ -9018,7 +9021,7 @@
         <v>610</v>
       </c>
       <c r="B527" s="14" t="s">
-        <v>625</v>
+        <v>95</v>
       </c>
       <c r="C527" s="14"/>
       <c r="D527" s="14"/>
@@ -9029,7 +9032,7 @@
         <v>610</v>
       </c>
       <c r="B528" s="14" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C528" s="14"/>
       <c r="D528" s="14"/>
@@ -9040,7 +9043,7 @@
         <v>610</v>
       </c>
       <c r="B529" s="14" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C529" s="14"/>
       <c r="D529" s="14"/>
@@ -9051,7 +9054,7 @@
         <v>610</v>
       </c>
       <c r="B530" s="14" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C530" s="14"/>
       <c r="D530" s="14"/>
@@ -9062,7 +9065,7 @@
         <v>610</v>
       </c>
       <c r="B531" s="14" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C531" s="14"/>
       <c r="D531" s="14"/>
@@ -9073,7 +9076,7 @@
         <v>610</v>
       </c>
       <c r="B532" s="14" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C532" s="14"/>
       <c r="D532" s="14"/>
@@ -9084,7 +9087,7 @@
         <v>610</v>
       </c>
       <c r="B533" s="14" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C533" s="14"/>
       <c r="D533" s="14"/>
@@ -9095,7 +9098,7 @@
         <v>610</v>
       </c>
       <c r="B534" s="14" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C534" s="14"/>
       <c r="D534" s="14"/>
@@ -9106,7 +9109,7 @@
         <v>610</v>
       </c>
       <c r="B535" s="14" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C535" s="14"/>
       <c r="D535" s="14"/>
@@ -9117,7 +9120,7 @@
         <v>610</v>
       </c>
       <c r="B536" s="14" t="s">
-        <v>705</v>
+        <v>633</v>
       </c>
       <c r="C536" s="14"/>
       <c r="D536" s="14"/>
@@ -9128,7 +9131,7 @@
         <v>610</v>
       </c>
       <c r="B537" s="14" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="C537" s="14"/>
       <c r="D537" s="14"/>
@@ -9139,7 +9142,7 @@
         <v>610</v>
       </c>
       <c r="B538" s="14" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="C538" s="14"/>
       <c r="D538" s="14"/>
@@ -9150,7 +9153,7 @@
         <v>610</v>
       </c>
       <c r="B539" s="14" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="C539" s="14"/>
       <c r="D539" s="14"/>
@@ -9161,7 +9164,7 @@
         <v>610</v>
       </c>
       <c r="B540" s="14" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="C540" s="14"/>
       <c r="D540" s="14"/>
@@ -9172,7 +9175,7 @@
         <v>610</v>
       </c>
       <c r="B541" s="14" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="C541" s="14"/>
       <c r="D541" s="14"/>
@@ -9183,7 +9186,7 @@
         <v>610</v>
       </c>
       <c r="B542" s="14" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C542" s="14"/>
       <c r="D542" s="14"/>
@@ -9194,7 +9197,7 @@
         <v>610</v>
       </c>
       <c r="B543" s="14" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="C543" s="14"/>
       <c r="D543" s="14"/>
@@ -9205,7 +9208,7 @@
         <v>610</v>
       </c>
       <c r="B544" s="14" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C544" s="14"/>
       <c r="D544" s="14"/>
@@ -9216,7 +9219,7 @@
         <v>610</v>
       </c>
       <c r="B545" s="14" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C545" s="14"/>
       <c r="D545" s="14"/>
@@ -9227,7 +9230,7 @@
         <v>610</v>
       </c>
       <c r="B546" s="14" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="C546" s="14"/>
       <c r="D546" s="14"/>
@@ -9238,7 +9241,7 @@
         <v>610</v>
       </c>
       <c r="B547" s="14" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="C547" s="14"/>
       <c r="D547" s="14"/>
@@ -9246,28 +9249,26 @@
     </row>
     <row r="548" spans="1:5" ht="15" thickBot="1">
       <c r="A548" s="14" t="s">
-        <v>634</v>
+        <v>610</v>
       </c>
       <c r="B548" s="14" t="s">
-        <v>635</v>
+        <v>716</v>
       </c>
       <c r="C548" s="14"/>
       <c r="D548" s="14"/>
-      <c r="E548" s="14" t="s">
-        <v>636</v>
-      </c>
+      <c r="E548" s="14"/>
     </row>
     <row r="549" spans="1:5" ht="15" thickBot="1">
       <c r="A549" s="14" t="s">
         <v>634</v>
       </c>
       <c r="B549" s="14" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="C549" s="14"/>
       <c r="D549" s="14"/>
       <c r="E549" s="14" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
     </row>
     <row r="550" spans="1:5" ht="15" thickBot="1">
@@ -9275,38 +9276,38 @@
         <v>634</v>
       </c>
       <c r="B550" s="14" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="C550" s="14"/>
       <c r="D550" s="14"/>
       <c r="E550" s="14" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="551" spans="1:5" ht="29.5" thickBot="1">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="551" spans="1:5" ht="15" thickBot="1">
       <c r="A551" s="14" t="s">
         <v>634</v>
       </c>
       <c r="B551" s="14" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="C551" s="14"/>
       <c r="D551" s="14"/>
       <c r="E551" s="14" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="552" spans="1:5" ht="15" thickBot="1">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="552" spans="1:5" ht="29.5" thickBot="1">
       <c r="A552" s="14" t="s">
         <v>634</v>
       </c>
       <c r="B552" s="14" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C552" s="14"/>
       <c r="D552" s="14"/>
       <c r="E552" s="14" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
     </row>
     <row r="553" spans="1:5" ht="15" thickBot="1">
@@ -9314,12 +9315,12 @@
         <v>634</v>
       </c>
       <c r="B553" s="14" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C553" s="14"/>
       <c r="D553" s="14"/>
       <c r="E553" s="14" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
     </row>
     <row r="554" spans="1:5" ht="15" thickBot="1">
@@ -9327,12 +9328,12 @@
         <v>634</v>
       </c>
       <c r="B554" s="14" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="C554" s="14"/>
       <c r="D554" s="14"/>
       <c r="E554" s="14" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
     </row>
     <row r="555" spans="1:5" ht="15" thickBot="1">
@@ -9340,12 +9341,12 @@
         <v>634</v>
       </c>
       <c r="B555" s="14" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="C555" s="14"/>
       <c r="D555" s="14"/>
       <c r="E555" s="14" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="556" spans="1:5" ht="15" thickBot="1">
@@ -9353,12 +9354,12 @@
         <v>634</v>
       </c>
       <c r="B556" s="14" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="C556" s="14"/>
       <c r="D556" s="14"/>
       <c r="E556" s="14" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
     </row>
     <row r="557" spans="1:5" ht="15" thickBot="1">
@@ -9366,38 +9367,38 @@
         <v>634</v>
       </c>
       <c r="B557" s="14" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="C557" s="14"/>
       <c r="D557" s="14"/>
       <c r="E557" s="14" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="558" spans="1:5" ht="29.5" thickBot="1">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="558" spans="1:5" ht="15" thickBot="1">
       <c r="A558" s="14" t="s">
         <v>634</v>
       </c>
       <c r="B558" s="14" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="C558" s="14"/>
       <c r="D558" s="14"/>
       <c r="E558" s="14" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="559" spans="1:5" ht="15" thickBot="1">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="559" spans="1:5" ht="29.5" thickBot="1">
       <c r="A559" s="14" t="s">
         <v>634</v>
       </c>
       <c r="B559" s="14" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C559" s="14"/>
       <c r="D559" s="14"/>
       <c r="E559" s="14" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
     </row>
     <row r="560" spans="1:5" ht="15" thickBot="1">
@@ -9405,18 +9406,20 @@
         <v>634</v>
       </c>
       <c r="B560" s="14" t="s">
-        <v>723</v>
+        <v>657</v>
       </c>
       <c r="C560" s="14"/>
       <c r="D560" s="14"/>
-      <c r="E560" s="14"/>
+      <c r="E560" s="14" t="s">
+        <v>658</v>
+      </c>
     </row>
     <row r="561" spans="1:5" ht="15" thickBot="1">
       <c r="A561" s="14" t="s">
         <v>634</v>
       </c>
       <c r="B561" s="14" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="C561" s="14"/>
       <c r="D561" s="14"/>
@@ -9427,7 +9430,7 @@
         <v>634</v>
       </c>
       <c r="B562" s="14" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="C562" s="14"/>
       <c r="D562" s="14"/>
@@ -9438,31 +9441,31 @@
         <v>634</v>
       </c>
       <c r="B563" s="14" t="s">
-        <v>30</v>
+        <v>725</v>
       </c>
       <c r="C563" s="14"/>
       <c r="D563" s="14"/>
-      <c r="E563" s="14" t="s">
-        <v>659</v>
-      </c>
+      <c r="E563" s="14"/>
     </row>
     <row r="564" spans="1:5" ht="15" thickBot="1">
       <c r="A564" s="14" t="s">
-        <v>660</v>
-      </c>
-      <c r="B564" s="13" t="s">
-        <v>146</v>
+        <v>634</v>
+      </c>
+      <c r="B564" s="14" t="s">
+        <v>30</v>
       </c>
       <c r="C564" s="14"/>
       <c r="D564" s="14"/>
-      <c r="E564" s="14"/>
+      <c r="E564" s="14" t="s">
+        <v>659</v>
+      </c>
     </row>
     <row r="565" spans="1:5" ht="15" thickBot="1">
       <c r="A565" s="14" t="s">
         <v>660</v>
       </c>
       <c r="B565" s="13" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C565" s="14"/>
       <c r="D565" s="14"/>
@@ -9473,7 +9476,7 @@
         <v>660</v>
       </c>
       <c r="B566" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C566" s="14"/>
       <c r="D566" s="14"/>
@@ -9484,7 +9487,7 @@
         <v>660</v>
       </c>
       <c r="B567" s="13" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C567" s="14"/>
       <c r="D567" s="14"/>
@@ -9495,7 +9498,7 @@
         <v>660</v>
       </c>
       <c r="B568" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C568" s="14"/>
       <c r="D568" s="14"/>
@@ -9506,7 +9509,7 @@
         <v>660</v>
       </c>
       <c r="B569" s="13" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C569" s="14"/>
       <c r="D569" s="14"/>
@@ -9517,7 +9520,7 @@
         <v>660</v>
       </c>
       <c r="B570" s="13" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C570" s="14"/>
       <c r="D570" s="14"/>
@@ -9528,7 +9531,7 @@
         <v>660</v>
       </c>
       <c r="B571" s="13" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C571" s="14"/>
       <c r="D571" s="14"/>
@@ -9539,7 +9542,7 @@
         <v>660</v>
       </c>
       <c r="B572" s="13" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C572" s="14"/>
       <c r="D572" s="14"/>
@@ -9550,7 +9553,7 @@
         <v>660</v>
       </c>
       <c r="B573" s="13" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C573" s="14"/>
       <c r="D573" s="14"/>
@@ -9561,7 +9564,7 @@
         <v>660</v>
       </c>
       <c r="B574" s="13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C574" s="14"/>
       <c r="D574" s="14"/>
@@ -9572,7 +9575,7 @@
         <v>660</v>
       </c>
       <c r="B575" s="13" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C575" s="14"/>
       <c r="D575" s="14"/>
@@ -9583,7 +9586,7 @@
         <v>660</v>
       </c>
       <c r="B576" s="13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C576" s="14"/>
       <c r="D576" s="14"/>
@@ -9594,7 +9597,7 @@
         <v>660</v>
       </c>
       <c r="B577" s="13" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C577" s="14"/>
       <c r="D577" s="14"/>
@@ -9605,7 +9608,7 @@
         <v>660</v>
       </c>
       <c r="B578" s="13" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C578" s="14"/>
       <c r="D578" s="14"/>
@@ -9616,7 +9619,7 @@
         <v>660</v>
       </c>
       <c r="B579" s="13" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C579" s="14"/>
       <c r="D579" s="14"/>
@@ -9627,7 +9630,7 @@
         <v>660</v>
       </c>
       <c r="B580" s="13" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C580" s="14"/>
       <c r="D580" s="14"/>
@@ -9638,7 +9641,7 @@
         <v>660</v>
       </c>
       <c r="B581" s="13" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C581" s="14"/>
       <c r="D581" s="14"/>
@@ -9649,7 +9652,7 @@
         <v>660</v>
       </c>
       <c r="B582" s="13" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C582" s="14"/>
       <c r="D582" s="14"/>
@@ -9660,7 +9663,7 @@
         <v>660</v>
       </c>
       <c r="B583" s="13" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C583" s="14"/>
       <c r="D583" s="14"/>
@@ -9671,7 +9674,7 @@
         <v>660</v>
       </c>
       <c r="B584" s="13" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C584" s="14"/>
       <c r="D584" s="14"/>
@@ -9682,7 +9685,7 @@
         <v>660</v>
       </c>
       <c r="B585" s="13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C585" s="14"/>
       <c r="D585" s="14"/>
@@ -9693,7 +9696,7 @@
         <v>660</v>
       </c>
       <c r="B586" s="13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C586" s="14"/>
       <c r="D586" s="14"/>
@@ -9704,7 +9707,7 @@
         <v>660</v>
       </c>
       <c r="B587" s="13" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C587" s="14"/>
       <c r="D587" s="14"/>
@@ -9715,7 +9718,7 @@
         <v>660</v>
       </c>
       <c r="B588" s="13" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C588" s="14"/>
       <c r="D588" s="14"/>
@@ -9726,7 +9729,7 @@
         <v>660</v>
       </c>
       <c r="B589" s="13" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C589" s="14"/>
       <c r="D589" s="14"/>
@@ -9737,7 +9740,7 @@
         <v>660</v>
       </c>
       <c r="B590" s="13" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C590" s="14"/>
       <c r="D590" s="14"/>
@@ -9748,7 +9751,7 @@
         <v>660</v>
       </c>
       <c r="B591" s="13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C591" s="14"/>
       <c r="D591" s="14"/>
@@ -9759,7 +9762,7 @@
         <v>660</v>
       </c>
       <c r="B592" s="13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C592" s="14"/>
       <c r="D592" s="14"/>
@@ -9770,7 +9773,7 @@
         <v>660</v>
       </c>
       <c r="B593" s="13" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C593" s="14"/>
       <c r="D593" s="14"/>
@@ -9781,7 +9784,7 @@
         <v>660</v>
       </c>
       <c r="B594" s="13" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C594" s="14"/>
       <c r="D594" s="14"/>
@@ -9792,7 +9795,7 @@
         <v>660</v>
       </c>
       <c r="B595" s="13" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C595" s="14"/>
       <c r="D595" s="14"/>
@@ -9803,7 +9806,7 @@
         <v>660</v>
       </c>
       <c r="B596" s="13" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C596" s="14"/>
       <c r="D596" s="14"/>
@@ -9814,7 +9817,7 @@
         <v>660</v>
       </c>
       <c r="B597" s="13" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C597" s="14"/>
       <c r="D597" s="14"/>
@@ -9825,7 +9828,7 @@
         <v>660</v>
       </c>
       <c r="B598" s="13" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C598" s="14"/>
       <c r="D598" s="14"/>
@@ -9836,7 +9839,7 @@
         <v>660</v>
       </c>
       <c r="B599" s="13" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C599" s="14"/>
       <c r="D599" s="14"/>
@@ -9847,7 +9850,7 @@
         <v>660</v>
       </c>
       <c r="B600" s="13" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C600" s="14"/>
       <c r="D600" s="14"/>
@@ -9858,7 +9861,7 @@
         <v>660</v>
       </c>
       <c r="B601" s="13" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C601" s="14"/>
       <c r="D601" s="14"/>
@@ -9869,7 +9872,7 @@
         <v>660</v>
       </c>
       <c r="B602" s="13" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C602" s="14"/>
       <c r="D602" s="14"/>
@@ -9880,7 +9883,7 @@
         <v>660</v>
       </c>
       <c r="B603" s="13" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C603" s="14"/>
       <c r="D603" s="14"/>
@@ -9891,7 +9894,7 @@
         <v>660</v>
       </c>
       <c r="B604" s="13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C604" s="14"/>
       <c r="D604" s="14"/>
@@ -9902,7 +9905,7 @@
         <v>660</v>
       </c>
       <c r="B605" s="13" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C605" s="14"/>
       <c r="D605" s="14"/>
@@ -9913,7 +9916,7 @@
         <v>660</v>
       </c>
       <c r="B606" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C606" s="14"/>
       <c r="D606" s="14"/>
@@ -9924,7 +9927,7 @@
         <v>660</v>
       </c>
       <c r="B607" s="13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C607" s="14"/>
       <c r="D607" s="14"/>
@@ -9935,7 +9938,7 @@
         <v>660</v>
       </c>
       <c r="B608" s="13" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C608" s="14"/>
       <c r="D608" s="14"/>
@@ -9946,7 +9949,7 @@
         <v>660</v>
       </c>
       <c r="B609" s="13" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C609" s="14"/>
       <c r="D609" s="14"/>
@@ -9957,7 +9960,7 @@
         <v>660</v>
       </c>
       <c r="B610" s="13" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C610" s="14"/>
       <c r="D610" s="14"/>
@@ -9968,7 +9971,7 @@
         <v>660</v>
       </c>
       <c r="B611" s="13" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C611" s="14"/>
       <c r="D611" s="14"/>
@@ -9979,7 +9982,7 @@
         <v>660</v>
       </c>
       <c r="B612" s="13" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C612" s="14"/>
       <c r="D612" s="14"/>
@@ -9990,7 +9993,7 @@
         <v>660</v>
       </c>
       <c r="B613" s="13" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C613" s="14"/>
       <c r="D613" s="14"/>
@@ -10001,7 +10004,7 @@
         <v>660</v>
       </c>
       <c r="B614" s="13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C614" s="14"/>
       <c r="D614" s="14"/>
@@ -10012,7 +10015,7 @@
         <v>660</v>
       </c>
       <c r="B615" s="13" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C615" s="14"/>
       <c r="D615" s="14"/>
@@ -10023,7 +10026,7 @@
         <v>660</v>
       </c>
       <c r="B616" s="13" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C616" s="14"/>
       <c r="D616" s="14"/>
@@ -10034,7 +10037,7 @@
         <v>660</v>
       </c>
       <c r="B617" s="13" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C617" s="14"/>
       <c r="D617" s="14"/>
@@ -10045,7 +10048,7 @@
         <v>660</v>
       </c>
       <c r="B618" s="13" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C618" s="14"/>
       <c r="D618" s="14"/>
@@ -10056,7 +10059,7 @@
         <v>660</v>
       </c>
       <c r="B619" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C619" s="14"/>
       <c r="D619" s="14"/>
@@ -10067,7 +10070,7 @@
         <v>660</v>
       </c>
       <c r="B620" s="13" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C620" s="14"/>
       <c r="D620" s="14"/>
@@ -10078,7 +10081,7 @@
         <v>660</v>
       </c>
       <c r="B621" s="13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C621" s="14"/>
       <c r="D621" s="14"/>
@@ -10089,7 +10092,7 @@
         <v>660</v>
       </c>
       <c r="B622" s="13" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C622" s="14"/>
       <c r="D622" s="14"/>
@@ -10100,7 +10103,7 @@
         <v>660</v>
       </c>
       <c r="B623" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C623" s="14"/>
       <c r="D623" s="14"/>
@@ -10111,7 +10114,7 @@
         <v>660</v>
       </c>
       <c r="B624" s="13" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C624" s="14"/>
       <c r="D624" s="14"/>
@@ -10122,7 +10125,7 @@
         <v>660</v>
       </c>
       <c r="B625" s="13" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C625" s="14"/>
       <c r="D625" s="14"/>
@@ -10133,7 +10136,7 @@
         <v>660</v>
       </c>
       <c r="B626" s="13" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C626" s="14"/>
       <c r="D626" s="14"/>
@@ -10144,7 +10147,7 @@
         <v>660</v>
       </c>
       <c r="B627" s="13" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C627" s="14"/>
       <c r="D627" s="14"/>
@@ -10155,7 +10158,7 @@
         <v>660</v>
       </c>
       <c r="B628" s="13" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C628" s="14"/>
       <c r="D628" s="14"/>
@@ -10166,7 +10169,7 @@
         <v>660</v>
       </c>
       <c r="B629" s="13" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C629" s="14"/>
       <c r="D629" s="14"/>
@@ -10177,7 +10180,7 @@
         <v>660</v>
       </c>
       <c r="B630" s="13" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C630" s="14"/>
       <c r="D630" s="14"/>
@@ -10188,7 +10191,7 @@
         <v>660</v>
       </c>
       <c r="B631" s="13" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C631" s="14"/>
       <c r="D631" s="14"/>
@@ -10199,7 +10202,7 @@
         <v>660</v>
       </c>
       <c r="B632" s="13" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C632" s="14"/>
       <c r="D632" s="14"/>
@@ -10210,7 +10213,7 @@
         <v>660</v>
       </c>
       <c r="B633" s="13" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C633" s="14"/>
       <c r="D633" s="14"/>
@@ -10221,7 +10224,7 @@
         <v>660</v>
       </c>
       <c r="B634" s="13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C634" s="14"/>
       <c r="D634" s="14"/>
@@ -10232,7 +10235,7 @@
         <v>660</v>
       </c>
       <c r="B635" s="13" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C635" s="14"/>
       <c r="D635" s="14"/>
@@ -10243,7 +10246,7 @@
         <v>660</v>
       </c>
       <c r="B636" s="13" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C636" s="14"/>
       <c r="D636" s="14"/>
@@ -10254,7 +10257,7 @@
         <v>660</v>
       </c>
       <c r="B637" s="13" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C637" s="14"/>
       <c r="D637" s="14"/>
@@ -10265,7 +10268,7 @@
         <v>660</v>
       </c>
       <c r="B638" s="13" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C638" s="14"/>
       <c r="D638" s="14"/>
@@ -10276,7 +10279,7 @@
         <v>660</v>
       </c>
       <c r="B639" s="13" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C639" s="14"/>
       <c r="D639" s="14"/>
@@ -10287,7 +10290,7 @@
         <v>660</v>
       </c>
       <c r="B640" s="13" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C640" s="14"/>
       <c r="D640" s="14"/>
@@ -10298,7 +10301,7 @@
         <v>660</v>
       </c>
       <c r="B641" s="13" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C641" s="14"/>
       <c r="D641" s="14"/>
@@ -10309,7 +10312,7 @@
         <v>660</v>
       </c>
       <c r="B642" s="13" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C642" s="14"/>
       <c r="D642" s="14"/>
@@ -10320,7 +10323,7 @@
         <v>660</v>
       </c>
       <c r="B643" s="13" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C643" s="14"/>
       <c r="D643" s="14"/>
@@ -10331,7 +10334,7 @@
         <v>660</v>
       </c>
       <c r="B644" s="13" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C644" s="14"/>
       <c r="D644" s="14"/>
@@ -10342,7 +10345,7 @@
         <v>660</v>
       </c>
       <c r="B645" s="13" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C645" s="14"/>
       <c r="D645" s="14"/>
@@ -10353,7 +10356,7 @@
         <v>660</v>
       </c>
       <c r="B646" s="13" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C646" s="14"/>
       <c r="D646" s="14"/>
@@ -10364,7 +10367,7 @@
         <v>660</v>
       </c>
       <c r="B647" s="13" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C647" s="14"/>
       <c r="D647" s="14"/>
@@ -10375,7 +10378,7 @@
         <v>660</v>
       </c>
       <c r="B648" s="13" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C648" s="14"/>
       <c r="D648" s="14"/>
@@ -10386,7 +10389,7 @@
         <v>660</v>
       </c>
       <c r="B649" s="13" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C649" s="14"/>
       <c r="D649" s="14"/>
@@ -10397,7 +10400,7 @@
         <v>660</v>
       </c>
       <c r="B650" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C650" s="14"/>
       <c r="D650" s="14"/>
@@ -10408,7 +10411,7 @@
         <v>660</v>
       </c>
       <c r="B651" s="13" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C651" s="14"/>
       <c r="D651" s="14"/>
@@ -10419,7 +10422,7 @@
         <v>660</v>
       </c>
       <c r="B652" s="13" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C652" s="14"/>
       <c r="D652" s="14"/>
@@ -10430,7 +10433,7 @@
         <v>660</v>
       </c>
       <c r="B653" s="13" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C653" s="14"/>
       <c r="D653" s="14"/>
@@ -10441,7 +10444,7 @@
         <v>660</v>
       </c>
       <c r="B654" s="13" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C654" s="14"/>
       <c r="D654" s="14"/>
@@ -10452,7 +10455,7 @@
         <v>660</v>
       </c>
       <c r="B655" s="13" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C655" s="14"/>
       <c r="D655" s="14"/>
@@ -10463,7 +10466,7 @@
         <v>660</v>
       </c>
       <c r="B656" s="13" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C656" s="14"/>
       <c r="D656" s="14"/>
@@ -10474,7 +10477,7 @@
         <v>660</v>
       </c>
       <c r="B657" s="13" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C657" s="14"/>
       <c r="D657" s="14"/>
@@ -10485,7 +10488,7 @@
         <v>660</v>
       </c>
       <c r="B658" s="13" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C658" s="14"/>
       <c r="D658" s="14"/>
@@ -10496,7 +10499,7 @@
         <v>660</v>
       </c>
       <c r="B659" s="13" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C659" s="14"/>
       <c r="D659" s="14"/>
@@ -10507,7 +10510,7 @@
         <v>660</v>
       </c>
       <c r="B660" s="13" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C660" s="14"/>
       <c r="D660" s="14"/>
@@ -10518,7 +10521,7 @@
         <v>660</v>
       </c>
       <c r="B661" s="13" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C661" s="14"/>
       <c r="D661" s="14"/>
@@ -10529,7 +10532,7 @@
         <v>660</v>
       </c>
       <c r="B662" s="13" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C662" s="14"/>
       <c r="D662" s="14"/>
@@ -10540,7 +10543,7 @@
         <v>660</v>
       </c>
       <c r="B663" s="13" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C663" s="14"/>
       <c r="D663" s="14"/>
@@ -10551,7 +10554,7 @@
         <v>660</v>
       </c>
       <c r="B664" s="13" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C664" s="14"/>
       <c r="D664" s="14"/>
@@ -10562,7 +10565,7 @@
         <v>660</v>
       </c>
       <c r="B665" s="13" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C665" s="14"/>
       <c r="D665" s="14"/>
@@ -10573,7 +10576,7 @@
         <v>660</v>
       </c>
       <c r="B666" s="13" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C666" s="14"/>
       <c r="D666" s="14"/>
@@ -10584,7 +10587,7 @@
         <v>660</v>
       </c>
       <c r="B667" s="13" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C667" s="14"/>
       <c r="D667" s="14"/>
@@ -10595,7 +10598,7 @@
         <v>660</v>
       </c>
       <c r="B668" s="13" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C668" s="14"/>
       <c r="D668" s="14"/>
@@ -10606,7 +10609,7 @@
         <v>660</v>
       </c>
       <c r="B669" s="13" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C669" s="14"/>
       <c r="D669" s="14"/>
@@ -10617,7 +10620,7 @@
         <v>660</v>
       </c>
       <c r="B670" s="13" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C670" s="14"/>
       <c r="D670" s="14"/>
@@ -10628,7 +10631,7 @@
         <v>660</v>
       </c>
       <c r="B671" s="13" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C671" s="14"/>
       <c r="D671" s="14"/>
@@ -10639,7 +10642,7 @@
         <v>660</v>
       </c>
       <c r="B672" s="13" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C672" s="14"/>
       <c r="D672" s="14"/>
@@ -10650,7 +10653,7 @@
         <v>660</v>
       </c>
       <c r="B673" s="13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C673" s="14"/>
       <c r="D673" s="14"/>
@@ -10661,7 +10664,7 @@
         <v>660</v>
       </c>
       <c r="B674" s="13" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C674" s="14"/>
       <c r="D674" s="14"/>
@@ -10672,7 +10675,7 @@
         <v>660</v>
       </c>
       <c r="B675" s="13" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C675" s="14"/>
       <c r="D675" s="14"/>
@@ -10683,7 +10686,7 @@
         <v>660</v>
       </c>
       <c r="B676" s="13" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C676" s="14"/>
       <c r="D676" s="14"/>
@@ -10694,7 +10697,7 @@
         <v>660</v>
       </c>
       <c r="B677" s="13" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C677" s="14"/>
       <c r="D677" s="14"/>
@@ -10705,7 +10708,7 @@
         <v>660</v>
       </c>
       <c r="B678" s="13" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C678" s="14"/>
       <c r="D678" s="14"/>
@@ -10716,7 +10719,7 @@
         <v>660</v>
       </c>
       <c r="B679" s="13" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C679" s="14"/>
       <c r="D679" s="14"/>
@@ -10727,7 +10730,7 @@
         <v>660</v>
       </c>
       <c r="B680" s="13" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C680" s="14"/>
       <c r="D680" s="14"/>
@@ -10738,7 +10741,7 @@
         <v>660</v>
       </c>
       <c r="B681" s="13" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C681" s="14"/>
       <c r="D681" s="14"/>
@@ -10749,7 +10752,7 @@
         <v>660</v>
       </c>
       <c r="B682" s="13" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C682" s="14"/>
       <c r="D682" s="14"/>
@@ -10760,7 +10763,7 @@
         <v>660</v>
       </c>
       <c r="B683" s="13" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C683" s="14"/>
       <c r="D683" s="14"/>
@@ -10771,7 +10774,7 @@
         <v>660</v>
       </c>
       <c r="B684" s="13" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C684" s="14"/>
       <c r="D684" s="14"/>
@@ -10782,7 +10785,7 @@
         <v>660</v>
       </c>
       <c r="B685" s="13" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C685" s="14"/>
       <c r="D685" s="14"/>
@@ -10793,7 +10796,7 @@
         <v>660</v>
       </c>
       <c r="B686" s="13" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C686" s="14"/>
       <c r="D686" s="14"/>
@@ -10804,7 +10807,7 @@
         <v>660</v>
       </c>
       <c r="B687" s="13" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C687" s="14"/>
       <c r="D687" s="14"/>
@@ -10815,7 +10818,7 @@
         <v>660</v>
       </c>
       <c r="B688" s="13" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C688" s="14"/>
       <c r="D688" s="14"/>
@@ -10826,7 +10829,7 @@
         <v>660</v>
       </c>
       <c r="B689" s="13" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C689" s="14"/>
       <c r="D689" s="14"/>
@@ -10837,7 +10840,7 @@
         <v>660</v>
       </c>
       <c r="B690" s="13" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C690" s="14"/>
       <c r="D690" s="14"/>
@@ -10848,7 +10851,7 @@
         <v>660</v>
       </c>
       <c r="B691" s="13" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C691" s="14"/>
       <c r="D691" s="14"/>
@@ -10859,7 +10862,7 @@
         <v>660</v>
       </c>
       <c r="B692" s="13" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C692" s="14"/>
       <c r="D692" s="14"/>
@@ -10870,7 +10873,7 @@
         <v>660</v>
       </c>
       <c r="B693" s="13" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C693" s="14"/>
       <c r="D693" s="14"/>
@@ -10881,7 +10884,7 @@
         <v>660</v>
       </c>
       <c r="B694" s="13" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C694" s="14"/>
       <c r="D694" s="14"/>
@@ -10892,7 +10895,7 @@
         <v>660</v>
       </c>
       <c r="B695" s="13" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C695" s="14"/>
       <c r="D695" s="14"/>
@@ -10903,7 +10906,7 @@
         <v>660</v>
       </c>
       <c r="B696" s="13" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C696" s="14"/>
       <c r="D696" s="14"/>
@@ -10914,7 +10917,7 @@
         <v>660</v>
       </c>
       <c r="B697" s="13" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C697" s="14"/>
       <c r="D697" s="14"/>
@@ -10925,7 +10928,7 @@
         <v>660</v>
       </c>
       <c r="B698" s="13" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C698" s="14"/>
       <c r="D698" s="14"/>
@@ -10936,7 +10939,7 @@
         <v>660</v>
       </c>
       <c r="B699" s="13" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C699" s="14"/>
       <c r="D699" s="14"/>
@@ -10947,7 +10950,7 @@
         <v>660</v>
       </c>
       <c r="B700" s="13" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C700" s="14"/>
       <c r="D700" s="14"/>
@@ -10958,7 +10961,7 @@
         <v>660</v>
       </c>
       <c r="B701" s="13" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C701" s="14"/>
       <c r="D701" s="14"/>
@@ -10969,7 +10972,7 @@
         <v>660</v>
       </c>
       <c r="B702" s="13" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C702" s="14"/>
       <c r="D702" s="14"/>
@@ -10980,7 +10983,7 @@
         <v>660</v>
       </c>
       <c r="B703" s="13" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C703" s="14"/>
       <c r="D703" s="14"/>
@@ -10991,7 +10994,7 @@
         <v>660</v>
       </c>
       <c r="B704" s="13" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C704" s="14"/>
       <c r="D704" s="14"/>
@@ -11002,7 +11005,7 @@
         <v>660</v>
       </c>
       <c r="B705" s="13" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C705" s="14"/>
       <c r="D705" s="14"/>
@@ -11013,7 +11016,7 @@
         <v>660</v>
       </c>
       <c r="B706" s="13" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C706" s="14"/>
       <c r="D706" s="14"/>
@@ -11024,7 +11027,7 @@
         <v>660</v>
       </c>
       <c r="B707" s="13" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C707" s="14"/>
       <c r="D707" s="14"/>
@@ -11035,7 +11038,7 @@
         <v>660</v>
       </c>
       <c r="B708" s="13" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C708" s="14"/>
       <c r="D708" s="14"/>
@@ -11046,7 +11049,7 @@
         <v>660</v>
       </c>
       <c r="B709" s="13" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C709" s="14"/>
       <c r="D709" s="14"/>
@@ -11057,7 +11060,7 @@
         <v>660</v>
       </c>
       <c r="B710" s="13" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C710" s="14"/>
       <c r="D710" s="14"/>
@@ -11068,7 +11071,7 @@
         <v>660</v>
       </c>
       <c r="B711" s="13" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C711" s="14"/>
       <c r="D711" s="14"/>
@@ -11079,7 +11082,7 @@
         <v>660</v>
       </c>
       <c r="B712" s="13" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C712" s="14"/>
       <c r="D712" s="14"/>
@@ -11090,7 +11093,7 @@
         <v>660</v>
       </c>
       <c r="B713" s="13" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C713" s="14"/>
       <c r="D713" s="14"/>
@@ -11101,7 +11104,7 @@
         <v>660</v>
       </c>
       <c r="B714" s="13" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C714" s="14"/>
       <c r="D714" s="14"/>
@@ -11112,7 +11115,7 @@
         <v>660</v>
       </c>
       <c r="B715" s="13" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C715" s="14"/>
       <c r="D715" s="14"/>
@@ -11123,7 +11126,7 @@
         <v>660</v>
       </c>
       <c r="B716" s="13" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C716" s="14"/>
       <c r="D716" s="14"/>
@@ -11134,7 +11137,7 @@
         <v>660</v>
       </c>
       <c r="B717" s="13" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C717" s="14"/>
       <c r="D717" s="14"/>
@@ -11145,7 +11148,7 @@
         <v>660</v>
       </c>
       <c r="B718" s="13" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C718" s="14"/>
       <c r="D718" s="14"/>
@@ -11156,7 +11159,7 @@
         <v>660</v>
       </c>
       <c r="B719" s="13" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C719" s="14"/>
       <c r="D719" s="14"/>
@@ -11167,7 +11170,7 @@
         <v>660</v>
       </c>
       <c r="B720" s="13" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C720" s="14"/>
       <c r="D720" s="14"/>
@@ -11178,7 +11181,7 @@
         <v>660</v>
       </c>
       <c r="B721" s="13" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C721" s="14"/>
       <c r="D721" s="14"/>
@@ -11189,7 +11192,7 @@
         <v>660</v>
       </c>
       <c r="B722" s="13" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C722" s="14"/>
       <c r="D722" s="14"/>
@@ -11200,7 +11203,7 @@
         <v>660</v>
       </c>
       <c r="B723" s="13" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C723" s="14"/>
       <c r="D723" s="14"/>
@@ -11211,7 +11214,7 @@
         <v>660</v>
       </c>
       <c r="B724" s="13" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C724" s="14"/>
       <c r="D724" s="14"/>
@@ -11222,7 +11225,7 @@
         <v>660</v>
       </c>
       <c r="B725" s="13" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C725" s="14"/>
       <c r="D725" s="14"/>
@@ -11233,7 +11236,7 @@
         <v>660</v>
       </c>
       <c r="B726" s="13" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C726" s="14"/>
       <c r="D726" s="14"/>
@@ -11244,7 +11247,7 @@
         <v>660</v>
       </c>
       <c r="B727" s="13" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C727" s="14"/>
       <c r="D727" s="14"/>
@@ -11255,7 +11258,7 @@
         <v>660</v>
       </c>
       <c r="B728" s="13" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C728" s="14"/>
       <c r="D728" s="14"/>
@@ -11266,7 +11269,7 @@
         <v>660</v>
       </c>
       <c r="B729" s="13" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C729" s="14"/>
       <c r="D729" s="14"/>
@@ -11277,7 +11280,7 @@
         <v>660</v>
       </c>
       <c r="B730" s="13" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C730" s="14"/>
       <c r="D730" s="14"/>
@@ -11288,7 +11291,7 @@
         <v>660</v>
       </c>
       <c r="B731" s="13" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C731" s="14"/>
       <c r="D731" s="14"/>
@@ -11299,7 +11302,7 @@
         <v>660</v>
       </c>
       <c r="B732" s="13" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C732" s="14"/>
       <c r="D732" s="14"/>
@@ -11310,7 +11313,7 @@
         <v>660</v>
       </c>
       <c r="B733" s="13" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C733" s="14"/>
       <c r="D733" s="14"/>
@@ -11321,7 +11324,7 @@
         <v>660</v>
       </c>
       <c r="B734" s="13" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C734" s="14"/>
       <c r="D734" s="14"/>
@@ -11332,7 +11335,7 @@
         <v>660</v>
       </c>
       <c r="B735" s="13" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C735" s="14"/>
       <c r="D735" s="14"/>
@@ -11343,7 +11346,7 @@
         <v>660</v>
       </c>
       <c r="B736" s="13" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C736" s="14"/>
       <c r="D736" s="14"/>
@@ -11354,7 +11357,7 @@
         <v>660</v>
       </c>
       <c r="B737" s="13" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C737" s="14"/>
       <c r="D737" s="14"/>
@@ -11365,7 +11368,7 @@
         <v>660</v>
       </c>
       <c r="B738" s="13" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C738" s="14"/>
       <c r="D738" s="14"/>
@@ -11376,7 +11379,7 @@
         <v>660</v>
       </c>
       <c r="B739" s="13" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C739" s="14"/>
       <c r="D739" s="14"/>
@@ -11387,7 +11390,7 @@
         <v>660</v>
       </c>
       <c r="B740" s="13" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C740" s="14"/>
       <c r="D740" s="14"/>
@@ -11398,7 +11401,7 @@
         <v>660</v>
       </c>
       <c r="B741" s="13" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C741" s="14"/>
       <c r="D741" s="14"/>
@@ -11409,7 +11412,7 @@
         <v>660</v>
       </c>
       <c r="B742" s="13" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C742" s="14"/>
       <c r="D742" s="14"/>
@@ -11420,7 +11423,7 @@
         <v>660</v>
       </c>
       <c r="B743" s="13" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C743" s="14"/>
       <c r="D743" s="14"/>
@@ -11431,7 +11434,7 @@
         <v>660</v>
       </c>
       <c r="B744" s="13" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C744" s="14"/>
       <c r="D744" s="14"/>
@@ -11442,7 +11445,7 @@
         <v>660</v>
       </c>
       <c r="B745" s="13" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C745" s="14"/>
       <c r="D745" s="14"/>
@@ -11453,7 +11456,7 @@
         <v>660</v>
       </c>
       <c r="B746" s="13" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C746" s="14"/>
       <c r="D746" s="14"/>
@@ -11464,7 +11467,7 @@
         <v>660</v>
       </c>
       <c r="B747" s="13" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C747" s="14"/>
       <c r="D747" s="14"/>
@@ -11475,7 +11478,7 @@
         <v>660</v>
       </c>
       <c r="B748" s="13" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C748" s="14"/>
       <c r="D748" s="14"/>
@@ -11486,7 +11489,7 @@
         <v>660</v>
       </c>
       <c r="B749" s="13" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C749" s="14"/>
       <c r="D749" s="14"/>
@@ -11497,7 +11500,7 @@
         <v>660</v>
       </c>
       <c r="B750" s="13" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C750" s="14"/>
       <c r="D750" s="14"/>
@@ -11508,7 +11511,7 @@
         <v>660</v>
       </c>
       <c r="B751" s="13" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C751" s="14"/>
       <c r="D751" s="14"/>
@@ -11519,7 +11522,7 @@
         <v>660</v>
       </c>
       <c r="B752" s="13" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C752" s="14"/>
       <c r="D752" s="14"/>
@@ -11530,7 +11533,7 @@
         <v>660</v>
       </c>
       <c r="B753" s="13" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C753" s="14"/>
       <c r="D753" s="14"/>
@@ -11541,7 +11544,7 @@
         <v>660</v>
       </c>
       <c r="B754" s="13" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C754" s="14"/>
       <c r="D754" s="14"/>
@@ -11552,7 +11555,7 @@
         <v>660</v>
       </c>
       <c r="B755" s="13" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C755" s="14"/>
       <c r="D755" s="14"/>
@@ -11563,7 +11566,7 @@
         <v>660</v>
       </c>
       <c r="B756" s="13" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C756" s="14"/>
       <c r="D756" s="14"/>
@@ -11574,7 +11577,7 @@
         <v>660</v>
       </c>
       <c r="B757" s="13" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C757" s="14"/>
       <c r="D757" s="14"/>
@@ -11585,7 +11588,7 @@
         <v>660</v>
       </c>
       <c r="B758" s="13" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C758" s="14"/>
       <c r="D758" s="14"/>
@@ -11596,7 +11599,7 @@
         <v>660</v>
       </c>
       <c r="B759" s="13" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C759" s="14"/>
       <c r="D759" s="14"/>
@@ -11607,7 +11610,7 @@
         <v>660</v>
       </c>
       <c r="B760" s="13" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C760" s="14"/>
       <c r="D760" s="14"/>
@@ -11618,7 +11621,7 @@
         <v>660</v>
       </c>
       <c r="B761" s="13" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C761" s="14"/>
       <c r="D761" s="14"/>
@@ -11629,7 +11632,7 @@
         <v>660</v>
       </c>
       <c r="B762" s="13" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C762" s="14"/>
       <c r="D762" s="14"/>
@@ -11640,7 +11643,7 @@
         <v>660</v>
       </c>
       <c r="B763" s="13" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C763" s="14"/>
       <c r="D763" s="14"/>
@@ -11651,7 +11654,7 @@
         <v>660</v>
       </c>
       <c r="B764" s="13" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C764" s="14"/>
       <c r="D764" s="14"/>
@@ -11662,7 +11665,7 @@
         <v>660</v>
       </c>
       <c r="B765" s="13" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C765" s="14"/>
       <c r="D765" s="14"/>
@@ -11673,7 +11676,7 @@
         <v>660</v>
       </c>
       <c r="B766" s="13" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C766" s="14"/>
       <c r="D766" s="14"/>
@@ -11684,7 +11687,7 @@
         <v>660</v>
       </c>
       <c r="B767" s="13" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C767" s="14"/>
       <c r="D767" s="14"/>
@@ -11695,7 +11698,7 @@
         <v>660</v>
       </c>
       <c r="B768" s="13" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C768" s="14"/>
       <c r="D768" s="14"/>
@@ -11706,7 +11709,7 @@
         <v>660</v>
       </c>
       <c r="B769" s="13" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C769" s="14"/>
       <c r="D769" s="14"/>
@@ -11717,7 +11720,7 @@
         <v>660</v>
       </c>
       <c r="B770" s="13" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C770" s="14"/>
       <c r="D770" s="14"/>
@@ -11728,7 +11731,7 @@
         <v>660</v>
       </c>
       <c r="B771" s="13" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C771" s="14"/>
       <c r="D771" s="14"/>
@@ -11739,7 +11742,7 @@
         <v>660</v>
       </c>
       <c r="B772" s="13" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C772" s="14"/>
       <c r="D772" s="14"/>
@@ -11750,7 +11753,7 @@
         <v>660</v>
       </c>
       <c r="B773" s="13" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C773" s="14"/>
       <c r="D773" s="14"/>
@@ -11761,7 +11764,7 @@
         <v>660</v>
       </c>
       <c r="B774" s="13" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C774" s="14"/>
       <c r="D774" s="14"/>
@@ -11772,7 +11775,7 @@
         <v>660</v>
       </c>
       <c r="B775" s="13" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C775" s="14"/>
       <c r="D775" s="14"/>
@@ -11783,7 +11786,7 @@
         <v>660</v>
       </c>
       <c r="B776" s="13" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C776" s="14"/>
       <c r="D776" s="14"/>
@@ -11794,7 +11797,7 @@
         <v>660</v>
       </c>
       <c r="B777" s="13" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C777" s="14"/>
       <c r="D777" s="14"/>
@@ -11805,7 +11808,7 @@
         <v>660</v>
       </c>
       <c r="B778" s="13" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C778" s="14"/>
       <c r="D778" s="14"/>
@@ -11816,7 +11819,7 @@
         <v>660</v>
       </c>
       <c r="B779" s="13" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C779" s="14"/>
       <c r="D779" s="14"/>
@@ -11827,7 +11830,7 @@
         <v>660</v>
       </c>
       <c r="B780" s="13" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C780" s="14"/>
       <c r="D780" s="14"/>
@@ -11838,7 +11841,7 @@
         <v>660</v>
       </c>
       <c r="B781" s="13" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C781" s="14"/>
       <c r="D781" s="14"/>
@@ -11849,7 +11852,7 @@
         <v>660</v>
       </c>
       <c r="B782" s="13" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C782" s="14"/>
       <c r="D782" s="14"/>
@@ -11860,7 +11863,7 @@
         <v>660</v>
       </c>
       <c r="B783" s="13" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C783" s="14"/>
       <c r="D783" s="14"/>
@@ -11871,7 +11874,7 @@
         <v>660</v>
       </c>
       <c r="B784" s="13" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C784" s="14"/>
       <c r="D784" s="14"/>
@@ -11882,7 +11885,7 @@
         <v>660</v>
       </c>
       <c r="B785" s="13" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C785" s="14"/>
       <c r="D785" s="14"/>
@@ -11893,7 +11896,7 @@
         <v>660</v>
       </c>
       <c r="B786" s="13" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C786" s="14"/>
       <c r="D786" s="14"/>
@@ -11904,7 +11907,7 @@
         <v>660</v>
       </c>
       <c r="B787" s="13" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C787" s="14"/>
       <c r="D787" s="14"/>
@@ -11915,7 +11918,7 @@
         <v>660</v>
       </c>
       <c r="B788" s="13" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C788" s="14"/>
       <c r="D788" s="14"/>
@@ -11926,7 +11929,7 @@
         <v>660</v>
       </c>
       <c r="B789" s="13" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C789" s="14"/>
       <c r="D789" s="14"/>
@@ -11937,7 +11940,7 @@
         <v>660</v>
       </c>
       <c r="B790" s="13" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C790" s="14"/>
       <c r="D790" s="14"/>
@@ -11948,7 +11951,7 @@
         <v>660</v>
       </c>
       <c r="B791" s="13" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C791" s="14"/>
       <c r="D791" s="14"/>
@@ -11959,7 +11962,7 @@
         <v>660</v>
       </c>
       <c r="B792" s="13" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C792" s="14"/>
       <c r="D792" s="14"/>
@@ -11970,7 +11973,7 @@
         <v>660</v>
       </c>
       <c r="B793" s="13" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C793" s="14"/>
       <c r="D793" s="14"/>
@@ -11981,7 +11984,7 @@
         <v>660</v>
       </c>
       <c r="B794" s="13" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C794" s="14"/>
       <c r="D794" s="14"/>
@@ -11992,7 +11995,7 @@
         <v>660</v>
       </c>
       <c r="B795" s="13" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C795" s="14"/>
       <c r="D795" s="14"/>
@@ -12003,7 +12006,7 @@
         <v>660</v>
       </c>
       <c r="B796" s="13" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C796" s="14"/>
       <c r="D796" s="14"/>
@@ -12014,7 +12017,7 @@
         <v>660</v>
       </c>
       <c r="B797" s="13" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C797" s="14"/>
       <c r="D797" s="14"/>
@@ -12025,7 +12028,7 @@
         <v>660</v>
       </c>
       <c r="B798" s="13" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C798" s="14"/>
       <c r="D798" s="14"/>
@@ -12036,7 +12039,7 @@
         <v>660</v>
       </c>
       <c r="B799" s="13" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C799" s="14"/>
       <c r="D799" s="14"/>
@@ -12047,7 +12050,7 @@
         <v>660</v>
       </c>
       <c r="B800" s="13" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C800" s="14"/>
       <c r="D800" s="14"/>
@@ -12058,7 +12061,7 @@
         <v>660</v>
       </c>
       <c r="B801" s="13" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C801" s="14"/>
       <c r="D801" s="14"/>
@@ -12069,7 +12072,7 @@
         <v>660</v>
       </c>
       <c r="B802" s="13" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C802" s="14"/>
       <c r="D802" s="14"/>
@@ -12080,7 +12083,7 @@
         <v>660</v>
       </c>
       <c r="B803" s="13" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C803" s="14"/>
       <c r="D803" s="14"/>
@@ -12091,7 +12094,7 @@
         <v>660</v>
       </c>
       <c r="B804" s="13" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C804" s="14"/>
       <c r="D804" s="14"/>
@@ -12102,7 +12105,7 @@
         <v>660</v>
       </c>
       <c r="B805" s="13" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C805" s="14"/>
       <c r="D805" s="14"/>
@@ -12113,7 +12116,7 @@
         <v>660</v>
       </c>
       <c r="B806" s="13" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C806" s="14"/>
       <c r="D806" s="14"/>
@@ -12124,7 +12127,7 @@
         <v>660</v>
       </c>
       <c r="B807" s="13" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C807" s="14"/>
       <c r="D807" s="14"/>
@@ -12135,7 +12138,7 @@
         <v>660</v>
       </c>
       <c r="B808" s="13" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C808" s="14"/>
       <c r="D808" s="14"/>
@@ -12146,7 +12149,7 @@
         <v>660</v>
       </c>
       <c r="B809" s="13" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C809" s="14"/>
       <c r="D809" s="14"/>
@@ -12157,7 +12160,7 @@
         <v>660</v>
       </c>
       <c r="B810" s="13" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C810" s="14"/>
       <c r="D810" s="14"/>
@@ -12168,7 +12171,7 @@
         <v>660</v>
       </c>
       <c r="B811" s="13" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C811" s="14"/>
       <c r="D811" s="14"/>
@@ -12179,7 +12182,7 @@
         <v>660</v>
       </c>
       <c r="B812" s="13" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C812" s="14"/>
       <c r="D812" s="14"/>
@@ -12190,7 +12193,7 @@
         <v>660</v>
       </c>
       <c r="B813" s="13" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C813" s="14"/>
       <c r="D813" s="14"/>
@@ -12201,7 +12204,7 @@
         <v>660</v>
       </c>
       <c r="B814" s="13" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C814" s="14"/>
       <c r="D814" s="14"/>
@@ -12212,18 +12215,22 @@
         <v>660</v>
       </c>
       <c r="B815" s="13" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C815" s="14"/>
       <c r="D815" s="14"/>
       <c r="E815" s="14"/>
     </row>
     <row r="816" spans="1:5" ht="15" thickBot="1">
-      <c r="A816" s="12"/>
-      <c r="B816" s="12"/>
-      <c r="C816" s="12"/>
-      <c r="D816" s="12"/>
-      <c r="E816" s="12"/>
+      <c r="A816" s="14" t="s">
+        <v>660</v>
+      </c>
+      <c r="B816" s="13" t="s">
+        <v>394</v>
+      </c>
+      <c r="C816" s="14"/>
+      <c r="D816" s="14"/>
+      <c r="E816" s="14"/>
     </row>
     <row r="817" spans="1:5" ht="15" thickBot="1">
       <c r="A817" s="12"/>

--- a/data/rules/pickLists.xlsx
+++ b/data/rules/pickLists.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hajibashi.Saba\Desktop\python-components\data\rules\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AA13435-3199-4011-BEE0-167F26CF8BFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0975A12-D7E9-4025-A626-A14A3E5D7123}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="760" windowWidth="13550" windowHeight="9670" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1100" yWindow="1100" windowWidth="13550" windowHeight="9670" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pick Lists" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2133" uniqueCount="755">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2141" uniqueCount="759">
   <si>
     <t>Path</t>
   </si>
@@ -2288,13 +2288,25 @@
   </si>
   <si>
     <t>People Involved</t>
+  </si>
+  <si>
+    <t>PDEA</t>
+  </si>
+  <si>
+    <t>Philippine Drug Enforcement Agency.</t>
+  </si>
+  <si>
+    <t>PDEA_MOST_WANTED</t>
+  </si>
+  <si>
+    <t>Most Wanted poster published by PDEA.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2329,6 +2341,12 @@
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF202B3B"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -2475,7 +2493,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2526,6 +2544,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -33412,8 +33433,36 @@
         <v>746</v>
       </c>
     </row>
-    <row r="1021" spans="1:5" s="4" customFormat="1" ht="12.5"/>
-    <row r="1022" spans="1:5" s="4" customFormat="1" ht="12.5"/>
+    <row r="1021" spans="1:5" ht="15" customHeight="1">
+      <c r="A1021" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1021" s="18" t="s">
+        <v>755</v>
+      </c>
+      <c r="C1021" s="18"/>
+      <c r="D1021" s="18"/>
+      <c r="E1021" s="18" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="1022" spans="1:5" ht="15" customHeight="1">
+      <c r="A1022" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1022" s="18" t="s">
+        <v>757</v>
+      </c>
+      <c r="C1022" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1022" s="18" t="s">
+        <v>755</v>
+      </c>
+      <c r="E1022" s="18" t="s">
+        <v>758</v>
+      </c>
+    </row>
     <row r="1023" spans="1:5" s="4" customFormat="1" ht="12.5"/>
     <row r="1024" spans="1:5" s="4" customFormat="1" ht="12.5"/>
     <row r="1025" spans="1:5" ht="12.5">

--- a/data/rules/pickLists.xlsx
+++ b/data/rules/pickLists.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hajibashi.Saba\Desktop\python-components\data\rules\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0975A12-D7E9-4025-A626-A14A3E5D7123}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{593DFC11-832D-41A5-8F9D-6672EE9B2B40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="1100" windowWidth="13550" windowHeight="9670" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="760" yWindow="760" windowWidth="13550" windowHeight="9670" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pick Lists" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2141" uniqueCount="759">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2167" uniqueCount="774">
   <si>
     <t>Path</t>
   </si>
@@ -2300,6 +2300,51 @@
   </si>
   <si>
     <t>Most Wanted poster published by PDEA.</t>
+  </si>
+  <si>
+    <t>PNP</t>
+  </si>
+  <si>
+    <t>Philippine National Police.</t>
+  </si>
+  <si>
+    <t>PNP_SDSPPO_MOST_WANTED</t>
+  </si>
+  <si>
+    <t>Reward posters published on the PNP SDSPPO Most Wanted Persons page.</t>
+  </si>
+  <si>
+    <t>Reward amount as printed. Currency and current availability are not inferred.</t>
+  </si>
+  <si>
+    <t>Joint Order Number</t>
+  </si>
+  <si>
+    <t>DND-DILG joint order reference from the JOR NO. field. It may be shared across persons.</t>
+  </si>
+  <si>
+    <t>Region as Listed</t>
+  </si>
+  <si>
+    <t>Region label as printed by the source. It is not a residence or nationality.</t>
+  </si>
+  <si>
+    <t>Position as Listed</t>
+  </si>
+  <si>
+    <t>Position or role described by the source, potentially historical. It is not asserted as current employment.</t>
+  </si>
+  <si>
+    <t>Case Reference</t>
+  </si>
+  <si>
+    <t>Court or case reference text as printed. It is not a unique person identifier.</t>
+  </si>
+  <si>
+    <t>Issuing Court</t>
+  </si>
+  <si>
+    <t>Issuing court text transcribed from the source. It is not a personal address.</t>
   </si>
 </sst>
 </file>
@@ -33463,56 +33508,120 @@
         <v>758</v>
       </c>
     </row>
-    <row r="1023" spans="1:5" s="4" customFormat="1" ht="12.5"/>
-    <row r="1024" spans="1:5" s="4" customFormat="1" ht="12.5"/>
-    <row r="1025" spans="1:5" ht="12.5">
-      <c r="A1025" s="4"/>
-      <c r="B1025" s="4"/>
-      <c r="C1025" s="4"/>
-      <c r="D1025" s="6"/>
-      <c r="E1025" s="4"/>
-    </row>
-    <row r="1026" spans="1:5" ht="12.5">
-      <c r="A1026" s="4"/>
-      <c r="B1026" s="4"/>
-      <c r="C1026" s="4"/>
-      <c r="D1026" s="6"/>
-      <c r="E1026" s="4"/>
-    </row>
-    <row r="1027" spans="1:5" ht="12.5">
-      <c r="A1027" s="4"/>
-      <c r="B1027" s="4"/>
-      <c r="C1027" s="4"/>
-      <c r="D1027" s="6"/>
-      <c r="E1027" s="4"/>
-    </row>
-    <row r="1028" spans="1:5" ht="12.5">
-      <c r="A1028" s="4"/>
-      <c r="B1028" s="4"/>
-      <c r="C1028" s="4"/>
-      <c r="D1028" s="6"/>
-      <c r="E1028" s="4"/>
-    </row>
-    <row r="1029" spans="1:5" ht="12.5">
-      <c r="A1029" s="4"/>
-      <c r="B1029" s="4"/>
-      <c r="C1029" s="4"/>
-      <c r="D1029" s="6"/>
-      <c r="E1029" s="4"/>
-    </row>
-    <row r="1030" spans="1:5" ht="12.5">
-      <c r="A1030" s="4"/>
-      <c r="B1030" s="4"/>
-      <c r="C1030" s="4"/>
-      <c r="D1030" s="6"/>
-      <c r="E1030" s="4"/>
-    </row>
-    <row r="1031" spans="1:5" ht="12.5">
-      <c r="A1031" s="4"/>
-      <c r="B1031" s="4"/>
-      <c r="C1031" s="4"/>
-      <c r="D1031" s="6"/>
-      <c r="E1031" s="4"/>
+    <row r="1023" spans="1:5" ht="15" customHeight="1">
+      <c r="A1023" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1023" s="18" t="s">
+        <v>759</v>
+      </c>
+      <c r="C1023" s="18"/>
+      <c r="D1023" s="18"/>
+      <c r="E1023" s="18" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="1024" spans="1:5" ht="15" customHeight="1">
+      <c r="A1024" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1024" s="18" t="s">
+        <v>761</v>
+      </c>
+      <c r="C1024" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1024" s="18" t="s">
+        <v>759</v>
+      </c>
+      <c r="E1024" s="18" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="1025" spans="1:5" ht="15" customHeight="1">
+      <c r="A1025" s="18" t="s">
+        <v>601</v>
+      </c>
+      <c r="B1025" s="18" t="s">
+        <v>627</v>
+      </c>
+      <c r="C1025" s="18"/>
+      <c r="D1025" s="18"/>
+      <c r="E1025" s="18" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="1026" spans="1:5" ht="15" customHeight="1">
+      <c r="A1026" s="18" t="s">
+        <v>601</v>
+      </c>
+      <c r="B1026" s="18" t="s">
+        <v>764</v>
+      </c>
+      <c r="C1026" s="18"/>
+      <c r="D1026" s="18"/>
+      <c r="E1026" s="18" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="1027" spans="1:5" ht="15" customHeight="1">
+      <c r="A1027" s="18" t="s">
+        <v>601</v>
+      </c>
+      <c r="B1027" s="18" t="s">
+        <v>766</v>
+      </c>
+      <c r="C1027" s="18"/>
+      <c r="D1027" s="18"/>
+      <c r="E1027" s="18" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="1028" spans="1:5" ht="15" customHeight="1">
+      <c r="A1028" s="18" t="s">
+        <v>601</v>
+      </c>
+      <c r="B1028" s="18" t="s">
+        <v>768</v>
+      </c>
+      <c r="C1028" s="18"/>
+      <c r="D1028" s="18"/>
+      <c r="E1028" s="18" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="1029" spans="1:5" ht="15" customHeight="1">
+      <c r="A1029" s="18" t="s">
+        <v>601</v>
+      </c>
+      <c r="B1029" s="18" t="s">
+        <v>770</v>
+      </c>
+      <c r="C1029" s="18"/>
+      <c r="D1029" s="18"/>
+      <c r="E1029" s="18" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="1030" spans="1:5" ht="15" customHeight="1">
+      <c r="A1030" s="18" t="s">
+        <v>601</v>
+      </c>
+      <c r="B1030" s="18" t="s">
+        <v>772</v>
+      </c>
+      <c r="C1030" s="18"/>
+      <c r="D1030" s="18"/>
+      <c r="E1030" s="18" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="1031" spans="1:5" ht="15" customHeight="1">
+      <c r="A1031" s="18"/>
+      <c r="B1031" s="18"/>
+      <c r="C1031" s="18"/>
+      <c r="D1031" s="18"/>
+      <c r="E1031" s="18"/>
     </row>
     <row r="1032" spans="1:5" ht="12.5">
       <c r="A1032" s="4"/>

--- a/data/rules/pickLists.xlsx
+++ b/data/rules/pickLists.xlsx
@@ -2577,7 +2577,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2628,6 +2628,12 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -33944,11 +33950,31 @@
       <c r="Z953" s="2"/>
     </row>
     <row r="954" spans="1:26" ht="15" thickBot="1">
-      <c r="A954" s="2"/>
-      <c r="B954" s="2"/>
-      <c r="C954" s="2"/>
-      <c r="D954" s="2"/>
-      <c r="E954" s="2"/>
+      <c r="A954" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sources.ListName</t>
+        </is>
+      </c>
+      <c r="B954" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PNP_MOST_WANTED_WITH_REWARDS_CRIMINALITY_2022</t>
+        </is>
+      </c>
+      <c r="C954" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sources.SourceName</t>
+        </is>
+      </c>
+      <c r="D954" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PNP</t>
+        </is>
+      </c>
+      <c r="E954" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Historical snapshot dated 13 October 2022. Wanted status and reward availability are as listed, not asserted as current.</t>
+        </is>
+      </c>
       <c r="F954" s="2"/>
       <c r="G954" s="2"/>
       <c r="H954" s="2"/>
@@ -33972,11 +33998,23 @@
       <c r="Z954" s="2"/>
     </row>
     <row r="955" spans="1:26" ht="15" thickBot="1">
-      <c r="A955" s="2"/>
-      <c r="B955" s="2"/>
+      <c r="A955" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">additionalInfo.Type</t>
+        </is>
+      </c>
+      <c r="B955" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DILG Memorandum Circular Number</t>
+        </is>
+      </c>
       <c r="C955" s="2"/>
       <c r="D955" s="2"/>
-      <c r="E955" s="2"/>
+      <c r="E955" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DILG circular number as printed in the historical source.</t>
+        </is>
+      </c>
       <c r="F955" s="2"/>
       <c r="G955" s="2"/>
       <c r="H955" s="2"/>
@@ -34000,11 +34038,23 @@
       <c r="Z955" s="2"/>
     </row>
     <row r="956" spans="1:26" ht="15" thickBot="1">
-      <c r="A956" s="2"/>
-      <c r="B956" s="2"/>
+      <c r="A956" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">additionalInfo.Type</t>
+        </is>
+      </c>
+      <c r="B956" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">List Reference Date</t>
+        </is>
+      </c>
       <c r="C956" s="2"/>
       <c r="D956" s="2"/>
-      <c r="E956" s="2"/>
+      <c r="E956" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reference date of the source snapshot, not the download date.</t>
+        </is>
+      </c>
       <c r="F956" s="2"/>
       <c r="G956" s="2"/>
       <c r="H956" s="2"/>
@@ -34028,11 +34078,23 @@
       <c r="Z956" s="2"/>
     </row>
     <row r="957" spans="1:26" ht="15" thickBot="1">
-      <c r="A957" s="2"/>
-      <c r="B957" s="2"/>
+      <c r="A957" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">additionalInfo.Type</t>
+        </is>
+      </c>
+      <c r="B957" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Identity Note</t>
+        </is>
+      </c>
       <c r="C957" s="2"/>
       <c r="D957" s="2"/>
-      <c r="E957" s="2"/>
+      <c r="E957" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Source identity limitations and fallback provenance.</t>
+        </is>
+      </c>
       <c r="F957" s="2"/>
       <c r="G957" s="2"/>
       <c r="H957" s="2"/>
